--- a/Data_Files/Driver_Wins.xlsx
+++ b/Data_Files/Driver_Wins.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BECED2-B30C-461D-8405-927002AD5609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED37B498-AC2D-4376-85A8-C7A4C62A33D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AD2">
+        <v>2</v>
+      </c>
       <c r="AE2">
         <v>6</v>
       </c>
@@ -1754,6 +1757,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
       <c r="AE3">
         <v>0</v>
       </c>
@@ -1784,8 +1790,12 @@
         <v>3</v>
       </c>
       <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
       <c r="AF4" s="1">
         <v>0</v>
       </c>
@@ -1812,6 +1822,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AD5">
+        <v>2</v>
+      </c>
       <c r="AE5">
         <v>1</v>
       </c>
@@ -1842,8 +1855,12 @@
         <v>5</v>
       </c>
       <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
       <c r="AF6" s="1">
         <v>0</v>
       </c>
@@ -1870,6 +1887,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
       <c r="AE7">
         <v>0</v>
       </c>
@@ -1901,8 +1921,12 @@
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
       <c r="AF8" s="1">
         <v>0</v>
       </c>
@@ -1929,8 +1953,12 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
       <c r="AF9" s="1">
         <v>0</v>
       </c>
@@ -1957,6 +1985,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
       <c r="AE10">
         <v>0</v>
       </c>
@@ -1986,6 +2017,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
       <c r="AE11">
         <v>0</v>
       </c>
@@ -2015,8 +2049,12 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
       <c r="AF12" s="1">
         <v>0</v>
       </c>
@@ -2043,6 +2081,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
       <c r="AE13">
         <v>0</v>
       </c>
@@ -2071,8 +2112,12 @@
       </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
+      </c>
       <c r="AF14" s="1">
         <v>0</v>
       </c>
@@ -2099,6 +2144,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
       <c r="AE15">
         <v>0</v>
       </c>
@@ -2128,7 +2176,12 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="AE16" s="1"/>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>0</v>
+      </c>
       <c r="AF16" s="1">
         <v>0</v>
       </c>
@@ -2155,6 +2208,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AD17">
+        <v>4</v>
+      </c>
       <c r="AE17">
         <v>0</v>
       </c>
@@ -2183,8 +2239,12 @@
       </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>0</v>
+      </c>
       <c r="AF18" s="1">
         <v>0</v>
       </c>
@@ -2213,8 +2273,12 @@
       </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>0</v>
+      </c>
       <c r="AF19" s="1">
         <v>0</v>
       </c>
@@ -2242,8 +2306,12 @@
         <v>18</v>
       </c>
       <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>0</v>
+      </c>
       <c r="AF20" s="1">
         <v>0</v>
       </c>
@@ -2271,8 +2339,12 @@
         <v>19</v>
       </c>
       <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>0</v>
+      </c>
       <c r="AF21" s="1">
         <v>0</v>
       </c>
@@ -2299,6 +2371,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AD22">
+        <v>2</v>
+      </c>
       <c r="AE22">
         <v>0</v>
       </c>
@@ -2328,6 +2403,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
       <c r="AE23">
         <v>0</v>
       </c>
@@ -2359,8 +2437,12 @@
       </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
       <c r="AF24" s="1">
         <v>0</v>
       </c>
@@ -2388,8 +2470,12 @@
         <v>44</v>
       </c>
       <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
+      <c r="AD25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>0</v>
+      </c>
       <c r="AF25" s="1">
         <v>0</v>
       </c>
@@ -2419,8 +2505,12 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>0</v>
+      </c>
       <c r="AF26" s="1">
         <v>0</v>
       </c>
@@ -2450,8 +2540,12 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>0</v>
+      </c>
       <c r="AF27" s="1">
         <v>0</v>
       </c>
@@ -2478,6 +2572,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
       <c r="AE28">
         <v>0</v>
       </c>
@@ -2510,8 +2607,12 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>0</v>
+      </c>
       <c r="AF29" s="1">
         <v>0</v>
       </c>
@@ -2541,8 +2642,12 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>0</v>
+      </c>
       <c r="AF30" s="1">
         <v>0</v>
       </c>
@@ -2570,8 +2675,12 @@
         <v>54</v>
       </c>
       <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
+      <c r="AD31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="1">
+        <v>0</v>
+      </c>
       <c r="AF31" s="1">
         <v>0</v>
       </c>
@@ -2601,8 +2710,12 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
+      <c r="AD32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>0</v>
+      </c>
       <c r="AF32" s="1">
         <v>0</v>
       </c>
@@ -2629,7 +2742,12 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
-      <c r="AE33" s="1"/>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>0</v>
+      </c>
       <c r="AF33" s="1">
         <v>0</v>
       </c>
@@ -2659,8 +2777,12 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>0</v>
+      </c>
       <c r="AF34" s="1">
         <v>0</v>
       </c>
@@ -2690,8 +2812,12 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>0</v>
+      </c>
       <c r="AF35" s="1">
         <v>0</v>
       </c>
@@ -2721,8 +2847,12 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>0</v>
+      </c>
       <c r="AF36" s="1">
         <v>0</v>
       </c>
@@ -2752,8 +2882,12 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
+      <c r="AD37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>0</v>
+      </c>
       <c r="AF37" s="1">
         <v>0</v>
       </c>
@@ -2783,8 +2917,12 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
+      <c r="AD38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>0</v>
+      </c>
       <c r="AF38" s="1">
         <v>0</v>
       </c>
@@ -2815,8 +2953,12 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>0</v>
+      </c>
       <c r="AF39" s="1">
         <v>0</v>
       </c>
@@ -2847,8 +2989,12 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
-      <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>0</v>
+      </c>
       <c r="AF40" s="1">
         <v>0</v>
       </c>
@@ -2875,7 +3021,9 @@
       <c r="A41" t="s">
         <v>64</v>
       </c>
-      <c r="AE41" s="1"/>
+      <c r="AE41" s="1">
+        <v>0</v>
+      </c>
       <c r="AF41" s="1">
         <v>0</v>
       </c>
@@ -2906,8 +3054,12 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>0</v>
+      </c>
       <c r="AF42" s="1">
         <v>0</v>
       </c>
@@ -2938,8 +3090,12 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>0</v>
+      </c>
       <c r="AF43" s="1">
         <v>0</v>
       </c>
@@ -2971,8 +3127,12 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="1">
+        <v>0</v>
+      </c>
       <c r="AF44" s="1">
         <v>0</v>
       </c>
@@ -3033,8 +3193,12 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1">
+        <v>0</v>
+      </c>
       <c r="AF46" s="1">
         <v>0</v>
       </c>
@@ -3066,8 +3230,12 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
-      <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1">
+        <v>0</v>
+      </c>
       <c r="AF47" s="1">
         <v>0</v>
       </c>
@@ -3099,8 +3267,12 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
-      <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>0</v>
+      </c>
       <c r="AF48" s="1">
         <v>0</v>
       </c>
@@ -3132,8 +3304,12 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
-      <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
+      <c r="AD49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="1">
+        <v>0</v>
+      </c>
       <c r="AF49" s="1">
         <v>0</v>
       </c>
@@ -3165,8 +3341,12 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
+      <c r="AD50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>0</v>
+      </c>
       <c r="AF50" s="1">
         <v>0</v>
       </c>
@@ -3199,8 +3379,12 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
-      <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1">
+        <v>0</v>
+      </c>
       <c r="AF51" s="1">
         <v>0</v>
       </c>
@@ -3233,8 +3417,12 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1">
+        <v>0</v>
+      </c>
       <c r="AF52" s="1">
         <v>0</v>
       </c>
@@ -3267,8 +3455,12 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
-      <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
+      <c r="AD53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1">
+        <v>0</v>
+      </c>
       <c r="AF53" s="1">
         <v>0</v>
       </c>
@@ -3301,8 +3493,12 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1">
+        <v>0</v>
+      </c>
       <c r="AF54" s="1">
         <v>0</v>
       </c>
@@ -3335,8 +3531,12 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
-      <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
+      <c r="AD55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1">
+        <v>0</v>
+      </c>
       <c r="AF55" s="1">
         <v>0</v>
       </c>
@@ -3369,8 +3569,12 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
+      <c r="AD56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1">
+        <v>0</v>
+      </c>
       <c r="AF56" s="1">
         <v>0</v>
       </c>
@@ -3404,8 +3608,12 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="1">
+        <v>0</v>
+      </c>
       <c r="AF57" s="1">
         <v>0</v>
       </c>
@@ -3439,8 +3647,12 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
+      <c r="AD58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="1">
+        <v>0</v>
+      </c>
       <c r="AF58" s="1">
         <v>0</v>
       </c>
@@ -3474,8 +3686,12 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
-      <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
+      <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1">
+        <v>0</v>
+      </c>
       <c r="AF59" s="1">
         <v>0</v>
       </c>
@@ -3509,8 +3725,12 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
-      <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="1">
+        <v>0</v>
+      </c>
       <c r="AF60" s="1">
         <v>0</v>
       </c>
@@ -3544,8 +3764,12 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
-      <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
+      <c r="AD61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="1">
+        <v>0</v>
+      </c>
       <c r="AF61" s="1">
         <v>0</v>
       </c>
@@ -3580,8 +3804,12 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
-      <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
+      <c r="AD62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="1">
+        <v>0</v>
+      </c>
       <c r="AF62" s="1">
         <v>0</v>
       </c>
@@ -3616,8 +3844,12 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
-      <c r="AD63" s="1"/>
-      <c r="AE63" s="1"/>
+      <c r="AD63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1">
+        <v>0</v>
+      </c>
       <c r="AF63" s="1">
         <v>0</v>
       </c>
@@ -3653,8 +3885,12 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
-      <c r="AD64" s="1"/>
-      <c r="AE64" s="1"/>
+      <c r="AD64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="1">
+        <v>0</v>
+      </c>
       <c r="AF64" s="1">
         <v>0</v>
       </c>
@@ -3690,8 +3926,12 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
-      <c r="AD65" s="1"/>
-      <c r="AE65" s="1"/>
+      <c r="AD65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="1">
+        <v>0</v>
+      </c>
       <c r="AF65" s="1">
         <v>0</v>
       </c>
@@ -3727,8 +3967,12 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
-      <c r="AD66" s="1"/>
-      <c r="AE66" s="1"/>
+      <c r="AD66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="1">
+        <v>0</v>
+      </c>
       <c r="AF66" s="1">
         <v>0</v>
       </c>
@@ -3764,8 +4008,12 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
-      <c r="AD67" s="1"/>
-      <c r="AE67" s="1"/>
+      <c r="AD67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="1">
+        <v>0</v>
+      </c>
       <c r="AF67" s="1">
         <v>0</v>
       </c>
@@ -3792,7 +4040,39 @@
       <c r="A68" t="s">
         <v>92</v>
       </c>
-      <c r="AE68" s="1"/>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="1">
+        <v>0</v>
+      </c>
       <c r="AF68" s="1">
         <v>0</v>
       </c>
@@ -3829,8 +4109,12 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
-      <c r="AD69" s="1"/>
-      <c r="AE69" s="1"/>
+      <c r="AD69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="1">
+        <v>0</v>
+      </c>
       <c r="AF69" s="1">
         <v>0</v>
       </c>
@@ -3867,8 +4151,12 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
-      <c r="AD70" s="1"/>
-      <c r="AE70" s="1"/>
+      <c r="AD70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1">
+        <v>0</v>
+      </c>
       <c r="AF70" s="1">
         <v>0</v>
       </c>
@@ -3905,8 +4193,12 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
-      <c r="AD71" s="1"/>
-      <c r="AE71" s="1"/>
+      <c r="AD71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="1">
+        <v>0</v>
+      </c>
       <c r="AF71" s="1">
         <v>0</v>
       </c>
@@ -3943,8 +4235,12 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
-      <c r="AD72" s="1"/>
-      <c r="AE72" s="1"/>
+      <c r="AD72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="1">
+        <v>0</v>
+      </c>
       <c r="AF72" s="1">
         <v>0</v>
       </c>
@@ -3981,8 +4277,12 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
-      <c r="AD73" s="1"/>
-      <c r="AE73" s="1"/>
+      <c r="AD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="1">
+        <v>0</v>
+      </c>
       <c r="AF73" s="1">
         <v>0</v>
       </c>
@@ -4020,8 +4320,12 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
-      <c r="AD74" s="1"/>
-      <c r="AE74" s="1"/>
+      <c r="AD74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1">
+        <v>0</v>
+      </c>
       <c r="AF74" s="1">
         <v>0</v>
       </c>
@@ -4059,8 +4363,12 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
-      <c r="AD75" s="1"/>
-      <c r="AE75" s="1"/>
+      <c r="AD75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>0</v>
+      </c>
       <c r="AF75" s="1">
         <v>0</v>
       </c>
@@ -4098,8 +4406,12 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
-      <c r="AD76" s="1"/>
-      <c r="AE76" s="1"/>
+      <c r="AD76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>0</v>
+      </c>
       <c r="AF76" s="1">
         <v>0</v>
       </c>
@@ -4137,8 +4449,12 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
-      <c r="AD77" s="1"/>
-      <c r="AE77" s="1"/>
+      <c r="AD77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>0</v>
+      </c>
       <c r="AF77" s="1">
         <v>0</v>
       </c>
@@ -4176,8 +4492,12 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
-      <c r="AD78" s="1"/>
-      <c r="AE78" s="1"/>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
       <c r="AF78" s="1">
         <v>0</v>
       </c>
@@ -4216,8 +4536,12 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
-      <c r="AD79" s="1"/>
-      <c r="AE79" s="1"/>
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>0</v>
+      </c>
       <c r="AF79" s="1">
         <v>0</v>
       </c>
@@ -4256,8 +4580,12 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
-      <c r="AD80" s="1"/>
-      <c r="AE80" s="1"/>
+      <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
       <c r="AF80" s="1">
         <v>0</v>
       </c>
@@ -4297,8 +4625,12 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
-      <c r="AD81" s="1"/>
-      <c r="AE81" s="1"/>
+      <c r="AD81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1">
+        <v>0</v>
+      </c>
       <c r="AF81" s="1">
         <v>0</v>
       </c>
@@ -4338,8 +4670,12 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
-      <c r="AD82" s="1"/>
-      <c r="AE82" s="1"/>
+      <c r="AD82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="1">
+        <v>0</v>
+      </c>
       <c r="AF82" s="1">
         <v>0</v>
       </c>
@@ -4379,8 +4715,12 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
-      <c r="AD83" s="1"/>
-      <c r="AE83" s="1"/>
+      <c r="AD83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1">
+        <v>0</v>
+      </c>
       <c r="AF83" s="1">
         <v>0</v>
       </c>
@@ -4420,8 +4760,12 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
-      <c r="AD84" s="1"/>
-      <c r="AE84" s="1"/>
+      <c r="AD84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="1">
+        <v>0</v>
+      </c>
       <c r="AF84" s="1">
         <v>0</v>
       </c>
@@ -4461,8 +4805,12 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
-      <c r="AD85" s="1"/>
-      <c r="AE85" s="1"/>
+      <c r="AD85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="1">
+        <v>0</v>
+      </c>
       <c r="AF85" s="1">
         <v>0</v>
       </c>
@@ -4503,8 +4851,12 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
-      <c r="AD86" s="1"/>
-      <c r="AE86" s="1"/>
+      <c r="AD86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="1">
+        <v>0</v>
+      </c>
       <c r="AF86" s="1">
         <v>0</v>
       </c>
@@ -4545,8 +4897,12 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
-      <c r="AD87" s="1"/>
-      <c r="AE87" s="1"/>
+      <c r="AD87" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="1">
+        <v>0</v>
+      </c>
       <c r="AF87" s="1">
         <v>0</v>
       </c>
@@ -4587,8 +4943,12 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
-      <c r="AD88" s="1"/>
-      <c r="AE88" s="1"/>
+      <c r="AD88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="1">
+        <v>0</v>
+      </c>
       <c r="AF88" s="1">
         <v>0</v>
       </c>
@@ -4629,8 +4989,12 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
-      <c r="AD89" s="1"/>
-      <c r="AE89" s="1"/>
+      <c r="AD89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="1">
+        <v>0</v>
+      </c>
       <c r="AF89" s="1">
         <v>0</v>
       </c>
@@ -4672,8 +5036,12 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
-      <c r="AD90" s="1"/>
-      <c r="AE90" s="1"/>
+      <c r="AD90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="1">
+        <v>0</v>
+      </c>
       <c r="AF90" s="1">
         <v>0</v>
       </c>
@@ -4715,8 +5083,12 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
-      <c r="AD91" s="1"/>
-      <c r="AE91" s="1"/>
+      <c r="AD91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="1">
+        <v>0</v>
+      </c>
       <c r="AF91" s="1">
         <v>0</v>
       </c>
@@ -4758,8 +5130,12 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
-      <c r="AD92" s="1"/>
-      <c r="AE92" s="1"/>
+      <c r="AD92" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="1">
+        <v>0</v>
+      </c>
       <c r="AF92" s="1">
         <v>0</v>
       </c>
@@ -4801,8 +5177,12 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
-      <c r="AD93" s="1"/>
-      <c r="AE93" s="1"/>
+      <c r="AD93" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="1">
+        <v>0</v>
+      </c>
       <c r="AF93" s="1">
         <v>0</v>
       </c>
@@ -4844,8 +5224,12 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
-      <c r="AD94" s="1"/>
-      <c r="AE94" s="1"/>
+      <c r="AD94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="1">
+        <v>0</v>
+      </c>
       <c r="AF94" s="1">
         <v>0</v>
       </c>
@@ -4888,8 +5272,12 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
-      <c r="AD95" s="1"/>
-      <c r="AE95" s="1"/>
+      <c r="AD95" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="1">
+        <v>0</v>
+      </c>
       <c r="AF95" s="1">
         <v>0</v>
       </c>
@@ -4932,8 +5320,12 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
-      <c r="AD96" s="1"/>
-      <c r="AE96" s="1"/>
+      <c r="AD96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="1">
+        <v>0</v>
+      </c>
       <c r="AF96" s="1">
         <v>0</v>
       </c>
@@ -4976,8 +5368,12 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
-      <c r="AD97" s="1"/>
-      <c r="AE97" s="1"/>
+      <c r="AD97" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="1">
+        <v>0</v>
+      </c>
       <c r="AF97" s="1">
         <v>0</v>
       </c>
@@ -5020,8 +5416,12 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
-      <c r="AD98" s="1"/>
-      <c r="AE98" s="1"/>
+      <c r="AD98" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="1">
+        <v>0</v>
+      </c>
       <c r="AF98" s="1">
         <v>0</v>
       </c>
@@ -5064,8 +5464,12 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
-      <c r="AD99" s="1"/>
-      <c r="AE99" s="1"/>
+      <c r="AD99" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="1">
+        <v>0</v>
+      </c>
       <c r="AF99" s="1">
         <v>0</v>
       </c>
@@ -5109,8 +5513,12 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
-      <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
+      <c r="AD100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="1">
+        <v>0</v>
+      </c>
       <c r="AF100" s="1">
         <v>0</v>
       </c>
@@ -5154,8 +5562,12 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
-      <c r="AD101" s="1"/>
-      <c r="AE101" s="1"/>
+      <c r="AD101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="1">
+        <v>0</v>
+      </c>
       <c r="AF101" s="1">
         <v>0</v>
       </c>
@@ -5199,8 +5611,12 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
-      <c r="AD102" s="1"/>
-      <c r="AE102" s="1"/>
+      <c r="AD102" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="1">
+        <v>0</v>
+      </c>
       <c r="AF102" s="1">
         <v>0</v>
       </c>
@@ -5244,8 +5660,12 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
-      <c r="AD103" s="1"/>
-      <c r="AE103" s="1"/>
+      <c r="AD103" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="1">
+        <v>0</v>
+      </c>
       <c r="AF103" s="1">
         <v>0</v>
       </c>
@@ -5290,8 +5710,12 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
-      <c r="AD104" s="1"/>
-      <c r="AE104" s="1"/>
+      <c r="AD104" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="1">
+        <v>0</v>
+      </c>
       <c r="AF104" s="1">
         <v>0</v>
       </c>
@@ -5336,8 +5760,12 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
-      <c r="AD105" s="1"/>
-      <c r="AE105" s="1"/>
+      <c r="AD105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="1">
+        <v>0</v>
+      </c>
       <c r="AF105" s="1">
         <v>0</v>
       </c>
@@ -5383,8 +5811,12 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
-      <c r="AD106" s="1"/>
-      <c r="AE106" s="1"/>
+      <c r="AD106" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="1">
+        <v>0</v>
+      </c>
       <c r="AF106" s="1">
         <v>0</v>
       </c>
@@ -5430,8 +5862,12 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
-      <c r="AD107" s="1"/>
-      <c r="AE107" s="1"/>
+      <c r="AD107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="1">
+        <v>0</v>
+      </c>
       <c r="AF107" s="1">
         <v>0</v>
       </c>
@@ -5477,8 +5913,12 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
-      <c r="AD108" s="1"/>
-      <c r="AE108" s="1"/>
+      <c r="AD108" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="1">
+        <v>0</v>
+      </c>
       <c r="AF108" s="1">
         <v>0</v>
       </c>
@@ -5525,8 +5965,12 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
-      <c r="AD109" s="1"/>
-      <c r="AE109" s="1"/>
+      <c r="AD109" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="1">
+        <v>0</v>
+      </c>
       <c r="AF109" s="1">
         <v>0</v>
       </c>
@@ -5573,8 +6017,12 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
-      <c r="AD110" s="1"/>
-      <c r="AE110" s="1"/>
+      <c r="AD110" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="1">
+        <v>0</v>
+      </c>
       <c r="AF110" s="1">
         <v>0</v>
       </c>
@@ -5621,8 +6069,12 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
-      <c r="AD111" s="1"/>
-      <c r="AE111" s="1"/>
+      <c r="AD111" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="1">
+        <v>0</v>
+      </c>
       <c r="AF111" s="1">
         <v>0</v>
       </c>
@@ -5670,8 +6122,12 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
-      <c r="AD112" s="1"/>
-      <c r="AE112" s="1"/>
+      <c r="AD112" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="1">
+        <v>0</v>
+      </c>
       <c r="AF112" s="1">
         <v>0</v>
       </c>
@@ -5719,8 +6175,12 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
-      <c r="AD113" s="1"/>
-      <c r="AE113" s="1"/>
+      <c r="AD113" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="1">
+        <v>0</v>
+      </c>
       <c r="AF113" s="1">
         <v>0</v>
       </c>
@@ -5768,8 +6228,12 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
-      <c r="AD114" s="1"/>
-      <c r="AE114" s="1"/>
+      <c r="AD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="1">
+        <v>0</v>
+      </c>
       <c r="AF114" s="1">
         <v>0</v>
       </c>
@@ -5818,8 +6282,12 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
-      <c r="AD115" s="1"/>
-      <c r="AE115" s="1"/>
+      <c r="AD115" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE115" s="1">
+        <v>0</v>
+      </c>
       <c r="AF115" s="1">
         <v>0</v>
       </c>
@@ -5868,8 +6336,12 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
-      <c r="AD116" s="1"/>
-      <c r="AE116" s="1"/>
+      <c r="AD116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="1">
+        <v>0</v>
+      </c>
       <c r="AF116" s="1">
         <v>0</v>
       </c>
@@ -5919,8 +6391,12 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
-      <c r="AD117" s="1"/>
-      <c r="AE117" s="1"/>
+      <c r="AD117" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="1">
+        <v>0</v>
+      </c>
       <c r="AF117" s="1">
         <v>0</v>
       </c>
@@ -5970,8 +6446,12 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
-      <c r="AD118" s="1"/>
-      <c r="AE118" s="1"/>
+      <c r="AD118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="1">
+        <v>0</v>
+      </c>
       <c r="AF118" s="1">
         <v>0</v>
       </c>
@@ -6021,8 +6501,12 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
-      <c r="AD119" s="1"/>
-      <c r="AE119" s="1"/>
+      <c r="AD119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="1">
+        <v>0</v>
+      </c>
       <c r="AF119" s="1">
         <v>0</v>
       </c>
@@ -6073,8 +6557,12 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
-      <c r="AD120" s="1"/>
-      <c r="AE120" s="1"/>
+      <c r="AD120" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE120" s="1">
+        <v>0</v>
+      </c>
       <c r="AF120" s="1">
         <v>0</v>
       </c>
@@ -6125,8 +6613,12 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
-      <c r="AD121" s="1"/>
-      <c r="AE121" s="1"/>
+      <c r="AD121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE121" s="1">
+        <v>0</v>
+      </c>
       <c r="AF121" s="1">
         <v>0</v>
       </c>
@@ -6177,8 +6669,12 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
-      <c r="AD122" s="1"/>
-      <c r="AE122" s="1"/>
+      <c r="AD122" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE122" s="1">
+        <v>0</v>
+      </c>
       <c r="AF122" s="1">
         <v>0</v>
       </c>
@@ -6230,8 +6726,12 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
-      <c r="AD123" s="1"/>
-      <c r="AE123" s="1"/>
+      <c r="AD123" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE123" s="1">
+        <v>0</v>
+      </c>
       <c r="AF123" s="1">
         <v>0</v>
       </c>
@@ -6283,8 +6783,12 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
-      <c r="AD124" s="1"/>
-      <c r="AE124" s="1"/>
+      <c r="AD124" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE124" s="1">
+        <v>0</v>
+      </c>
       <c r="AF124" s="1">
         <v>0</v>
       </c>
@@ -6336,8 +6840,12 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
-      <c r="AD125" s="1"/>
-      <c r="AE125" s="1"/>
+      <c r="AD125" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE125" s="1">
+        <v>0</v>
+      </c>
       <c r="AF125" s="1">
         <v>0</v>
       </c>
@@ -6390,8 +6898,12 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
-      <c r="AD126" s="1"/>
-      <c r="AE126" s="1"/>
+      <c r="AD126" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE126" s="1">
+        <v>0</v>
+      </c>
       <c r="AF126" s="1">
         <v>0</v>
       </c>
@@ -6422,12 +6934,1038 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B18" si="0">SUM(C3:R3)</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data_Files/Driver_Wins.xlsx
+++ b/Data_Files/Driver_Wins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED37B498-AC2D-4376-85A8-C7A4C62A33D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0597C2-6571-441D-892F-CA87B515ADF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Wins" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AC2">
+        <v>9</v>
+      </c>
       <c r="AD2">
         <v>2</v>
       </c>
@@ -1757,6 +1760,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AC3">
+        <v>1</v>
+      </c>
       <c r="AD3">
         <v>0</v>
       </c>
@@ -1789,7 +1795,9 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="AC4" s="1"/>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
       <c r="AD4" s="1">
         <v>0</v>
       </c>
@@ -1822,6 +1830,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AC5">
+        <v>3</v>
+      </c>
       <c r="AD5">
         <v>2</v>
       </c>
@@ -1854,7 +1865,9 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="AC6" s="1"/>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
       <c r="AD6" s="1">
         <v>0</v>
       </c>
@@ -1887,6 +1900,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
       <c r="AD7">
         <v>0</v>
       </c>
@@ -1920,7 +1936,9 @@
         <v>7</v>
       </c>
       <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
       <c r="AD8" s="1">
         <v>0</v>
       </c>
@@ -1953,6 +1971,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
       <c r="AD9" s="1">
         <v>0</v>
       </c>
@@ -1985,6 +2006,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
       <c r="AD10">
         <v>0</v>
       </c>
@@ -2017,6 +2041,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
       <c r="AD11">
         <v>0</v>
       </c>
@@ -2049,6 +2076,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
       <c r="AD12" s="1">
         <v>0</v>
       </c>
@@ -2081,6 +2111,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
       <c r="AD13">
         <v>0</v>
       </c>
@@ -2111,7 +2144,9 @@
         <v>13</v>
       </c>
       <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
       <c r="AD14" s="1">
         <v>0</v>
       </c>
@@ -2144,6 +2179,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
       <c r="AD15">
         <v>0</v>
       </c>
@@ -2176,6 +2214,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
       <c r="AD16">
         <v>0</v>
       </c>
@@ -2208,6 +2249,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
       <c r="AD17">
         <v>4</v>
       </c>
@@ -2238,7 +2282,9 @@
         <v>17</v>
       </c>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
+      <c r="AC18" s="1">
+        <v>0</v>
+      </c>
       <c r="AD18" s="1">
         <v>0</v>
       </c>
@@ -2272,7 +2318,9 @@
         <v>85</v>
       </c>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
+      <c r="AC19" s="1">
+        <v>0</v>
+      </c>
       <c r="AD19" s="1">
         <v>0</v>
       </c>
@@ -2305,7 +2353,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="AC20" s="1"/>
+      <c r="AC20" s="1">
+        <v>0</v>
+      </c>
       <c r="AD20" s="1">
         <v>0</v>
       </c>
@@ -2338,7 +2388,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="AC21" s="1"/>
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
       <c r="AD21" s="1">
         <v>0</v>
       </c>
@@ -2371,6 +2423,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
       <c r="AD22">
         <v>2</v>
       </c>
@@ -2403,6 +2458,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
       <c r="AD23">
         <v>0</v>
       </c>
@@ -2436,7 +2494,9 @@
         <v>22</v>
       </c>
       <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
       <c r="AD24" s="1">
         <v>0</v>
       </c>
@@ -2469,7 +2529,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
-      <c r="AC25" s="1"/>
+      <c r="AC25" s="1">
+        <v>0</v>
+      </c>
       <c r="AD25" s="1">
         <v>0</v>
       </c>
@@ -2504,7 +2566,9 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
+      <c r="AC26" s="1">
+        <v>0</v>
+      </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
@@ -2539,7 +2603,9 @@
       </c>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
+      <c r="AC27" s="1">
+        <v>0</v>
+      </c>
       <c r="AD27" s="1">
         <v>0</v>
       </c>
@@ -2572,6 +2638,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
       <c r="AD28">
         <v>0</v>
       </c>
@@ -2606,7 +2675,9 @@
       </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
+      <c r="AC29" s="1">
+        <v>0</v>
+      </c>
       <c r="AD29" s="1">
         <v>0</v>
       </c>
@@ -2641,7 +2712,9 @@
       </c>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
+      <c r="AC30" s="1">
+        <v>0</v>
+      </c>
       <c r="AD30" s="1">
         <v>0</v>
       </c>
@@ -2674,7 +2747,9 @@
       <c r="A31" t="s">
         <v>54</v>
       </c>
-      <c r="AC31" s="1"/>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
       <c r="AD31" s="1">
         <v>0</v>
       </c>
@@ -2709,7 +2784,9 @@
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
+      <c r="AC32" s="1">
+        <v>0</v>
+      </c>
       <c r="AD32" s="1">
         <v>0</v>
       </c>
@@ -2742,6 +2819,9 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
       <c r="AD33">
         <v>0</v>
       </c>
@@ -2776,7 +2856,9 @@
       </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
+      <c r="AC34" s="1">
+        <v>0</v>
+      </c>
       <c r="AD34" s="1">
         <v>0</v>
       </c>
@@ -2811,7 +2893,9 @@
       </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
+      <c r="AC35" s="1">
+        <v>0</v>
+      </c>
       <c r="AD35" s="1">
         <v>0</v>
       </c>
@@ -2846,7 +2930,9 @@
       </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
+      <c r="AC36" s="1">
+        <v>0</v>
+      </c>
       <c r="AD36" s="1">
         <v>0</v>
       </c>
@@ -2881,7 +2967,9 @@
       </c>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
+      <c r="AC37" s="1">
+        <v>0</v>
+      </c>
       <c r="AD37" s="1">
         <v>0</v>
       </c>
@@ -2916,7 +3004,9 @@
       </c>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
+      <c r="AC38" s="1">
+        <v>0</v>
+      </c>
       <c r="AD38" s="1">
         <v>0</v>
       </c>
@@ -2952,7 +3042,9 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
@@ -2988,7 +3080,9 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
+      <c r="AC40" s="1">
+        <v>0</v>
+      </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
@@ -3021,6 +3115,9 @@
       <c r="A41" t="s">
         <v>64</v>
       </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
       <c r="AE41" s="1">
         <v>0</v>
       </c>
@@ -3053,7 +3150,9 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
+      <c r="AC42" s="1">
+        <v>0</v>
+      </c>
       <c r="AD42" s="1">
         <v>0</v>
       </c>
@@ -3089,7 +3188,9 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
       <c r="AD43" s="1">
         <v>0</v>
       </c>
@@ -3126,7 +3227,9 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
+      <c r="AC44" s="1">
+        <v>0</v>
+      </c>
       <c r="AD44" s="1">
         <v>0</v>
       </c>
@@ -3158,6 +3261,9 @@
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
       </c>
       <c r="AE45">
         <v>0</v>
@@ -3192,7 +3298,9 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
+      <c r="AC46" s="1">
+        <v>0</v>
+      </c>
       <c r="AD46" s="1">
         <v>0</v>
       </c>
@@ -3229,7 +3337,9 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
-      <c r="AC47" s="1"/>
+      <c r="AC47" s="1">
+        <v>0</v>
+      </c>
       <c r="AD47" s="1">
         <v>0</v>
       </c>
@@ -3266,7 +3376,9 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
-      <c r="AC48" s="1"/>
+      <c r="AC48" s="1">
+        <v>0</v>
+      </c>
       <c r="AD48" s="1">
         <v>0</v>
       </c>
@@ -3303,7 +3415,9 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
-      <c r="AC49" s="1"/>
+      <c r="AC49" s="1">
+        <v>0</v>
+      </c>
       <c r="AD49" s="1">
         <v>0</v>
       </c>
@@ -3340,7 +3454,9 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
+      <c r="AC50" s="1">
+        <v>0</v>
+      </c>
       <c r="AD50" s="1">
         <v>0</v>
       </c>
@@ -3378,7 +3494,9 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
+      <c r="AC51" s="1">
+        <v>0</v>
+      </c>
       <c r="AD51" s="1">
         <v>0</v>
       </c>
@@ -3416,7 +3534,9 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
+      <c r="AC52" s="1">
+        <v>0</v>
+      </c>
       <c r="AD52" s="1">
         <v>0</v>
       </c>
@@ -3454,7 +3574,9 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
-      <c r="AC53" s="1"/>
+      <c r="AC53" s="1">
+        <v>0</v>
+      </c>
       <c r="AD53" s="1">
         <v>0</v>
       </c>
@@ -3492,7 +3614,9 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
+      <c r="AC54" s="1">
+        <v>0</v>
+      </c>
       <c r="AD54" s="1">
         <v>0</v>
       </c>
@@ -3530,7 +3654,9 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-      <c r="AC55" s="1"/>
+      <c r="AC55" s="1">
+        <v>0</v>
+      </c>
       <c r="AD55" s="1">
         <v>0</v>
       </c>
@@ -3568,7 +3694,9 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
+      <c r="AC56" s="1">
+        <v>0</v>
+      </c>
       <c r="AD56" s="1">
         <v>0</v>
       </c>
@@ -3607,7 +3735,9 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
+      <c r="AC57" s="1">
+        <v>0</v>
+      </c>
       <c r="AD57" s="1">
         <v>0</v>
       </c>
@@ -3646,7 +3776,9 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
+      <c r="AC58" s="1">
+        <v>0</v>
+      </c>
       <c r="AD58" s="1">
         <v>0</v>
       </c>
@@ -3685,7 +3817,9 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
-      <c r="AC59" s="1"/>
+      <c r="AC59" s="1">
+        <v>0</v>
+      </c>
       <c r="AD59" s="1">
         <v>0</v>
       </c>
@@ -3724,7 +3858,9 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
-      <c r="AC60" s="1"/>
+      <c r="AC60" s="1">
+        <v>0</v>
+      </c>
       <c r="AD60" s="1">
         <v>0</v>
       </c>
@@ -3763,7 +3899,9 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
-      <c r="AC61" s="1"/>
+      <c r="AC61" s="1">
+        <v>0</v>
+      </c>
       <c r="AD61" s="1">
         <v>0</v>
       </c>
@@ -3803,7 +3941,9 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
-      <c r="AC62" s="1"/>
+      <c r="AC62" s="1">
+        <v>0</v>
+      </c>
       <c r="AD62" s="1">
         <v>0</v>
       </c>
@@ -3843,7 +3983,9 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
-      <c r="AC63" s="1"/>
+      <c r="AC63" s="1">
+        <v>0</v>
+      </c>
       <c r="AD63" s="1">
         <v>0</v>
       </c>
@@ -3884,7 +4026,9 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
-      <c r="AC64" s="1"/>
+      <c r="AC64" s="1">
+        <v>0</v>
+      </c>
       <c r="AD64" s="1">
         <v>0</v>
       </c>
@@ -3925,7 +4069,9 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
-      <c r="AC65" s="1"/>
+      <c r="AC65" s="1">
+        <v>0</v>
+      </c>
       <c r="AD65" s="1">
         <v>0</v>
       </c>
@@ -3966,7 +4112,9 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
-      <c r="AC66" s="1"/>
+      <c r="AC66" s="1">
+        <v>0</v>
+      </c>
       <c r="AD66" s="1">
         <v>0</v>
       </c>
@@ -4007,7 +4155,9 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
-      <c r="AC67" s="1"/>
+      <c r="AC67" s="1">
+        <v>0</v>
+      </c>
       <c r="AD67" s="1">
         <v>0</v>
       </c>
@@ -4108,7 +4258,9 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
-      <c r="AC69" s="1"/>
+      <c r="AC69" s="1">
+        <v>0</v>
+      </c>
       <c r="AD69" s="1">
         <v>0</v>
       </c>
@@ -4150,7 +4302,9 @@
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
-      <c r="AC70" s="1"/>
+      <c r="AC70" s="1">
+        <v>0</v>
+      </c>
       <c r="AD70" s="1">
         <v>0</v>
       </c>
@@ -4192,7 +4346,9 @@
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
-      <c r="AC71" s="1"/>
+      <c r="AC71" s="1">
+        <v>0</v>
+      </c>
       <c r="AD71" s="1">
         <v>0</v>
       </c>
@@ -4234,7 +4390,9 @@
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
-      <c r="AC72" s="1"/>
+      <c r="AC72" s="1">
+        <v>0</v>
+      </c>
       <c r="AD72" s="1">
         <v>0</v>
       </c>
@@ -4276,7 +4434,9 @@
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
-      <c r="AC73" s="1"/>
+      <c r="AC73" s="1">
+        <v>0</v>
+      </c>
       <c r="AD73" s="1">
         <v>0</v>
       </c>
@@ -4319,7 +4479,9 @@
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
-      <c r="AC74" s="1"/>
+      <c r="AC74" s="1">
+        <v>0</v>
+      </c>
       <c r="AD74" s="1">
         <v>0</v>
       </c>
@@ -4362,7 +4524,9 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
-      <c r="AC75" s="1"/>
+      <c r="AC75" s="1">
+        <v>0</v>
+      </c>
       <c r="AD75" s="1">
         <v>0</v>
       </c>
@@ -4405,7 +4569,9 @@
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
-      <c r="AC76" s="1"/>
+      <c r="AC76" s="1">
+        <v>0</v>
+      </c>
       <c r="AD76" s="1">
         <v>0</v>
       </c>
@@ -4448,7 +4614,9 @@
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
-      <c r="AC77" s="1"/>
+      <c r="AC77" s="1">
+        <v>0</v>
+      </c>
       <c r="AD77" s="1">
         <v>0</v>
       </c>
@@ -4491,7 +4659,9 @@
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
-      <c r="AC78" s="1"/>
+      <c r="AC78" s="1">
+        <v>0</v>
+      </c>
       <c r="AD78" s="1">
         <v>0</v>
       </c>
@@ -4535,7 +4705,9 @@
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
-      <c r="AC79" s="1"/>
+      <c r="AC79" s="1">
+        <v>0</v>
+      </c>
       <c r="AD79" s="1">
         <v>0</v>
       </c>
@@ -4579,7 +4751,9 @@
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
-      <c r="AC80" s="1"/>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
       <c r="AD80" s="1">
         <v>0</v>
       </c>
@@ -4624,7 +4798,9 @@
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
-      <c r="AC81" s="1"/>
+      <c r="AC81" s="1">
+        <v>0</v>
+      </c>
       <c r="AD81" s="1">
         <v>0</v>
       </c>
@@ -4669,7 +4845,9 @@
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
-      <c r="AC82" s="1"/>
+      <c r="AC82" s="1">
+        <v>0</v>
+      </c>
       <c r="AD82" s="1">
         <v>0</v>
       </c>
@@ -4714,7 +4892,9 @@
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
-      <c r="AC83" s="1"/>
+      <c r="AC83" s="1">
+        <v>0</v>
+      </c>
       <c r="AD83" s="1">
         <v>0</v>
       </c>
@@ -4759,7 +4939,9 @@
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
-      <c r="AC84" s="1"/>
+      <c r="AC84" s="1">
+        <v>0</v>
+      </c>
       <c r="AD84" s="1">
         <v>0</v>
       </c>
@@ -4804,7 +4986,9 @@
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
-      <c r="AC85" s="1"/>
+      <c r="AC85" s="1">
+        <v>0</v>
+      </c>
       <c r="AD85" s="1">
         <v>0</v>
       </c>
@@ -4850,7 +5034,9 @@
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
-      <c r="AC86" s="1"/>
+      <c r="AC86" s="1">
+        <v>0</v>
+      </c>
       <c r="AD86" s="1">
         <v>0</v>
       </c>
@@ -4896,7 +5082,9 @@
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
-      <c r="AC87" s="1"/>
+      <c r="AC87" s="1">
+        <v>0</v>
+      </c>
       <c r="AD87" s="1">
         <v>0</v>
       </c>
@@ -4942,7 +5130,9 @@
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
-      <c r="AC88" s="1"/>
+      <c r="AC88" s="1">
+        <v>0</v>
+      </c>
       <c r="AD88" s="1">
         <v>0</v>
       </c>
@@ -4988,7 +5178,9 @@
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
-      <c r="AC89" s="1"/>
+      <c r="AC89" s="1">
+        <v>0</v>
+      </c>
       <c r="AD89" s="1">
         <v>0</v>
       </c>
@@ -5035,7 +5227,9 @@
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
-      <c r="AC90" s="1"/>
+      <c r="AC90" s="1">
+        <v>0</v>
+      </c>
       <c r="AD90" s="1">
         <v>0</v>
       </c>
@@ -5082,7 +5276,9 @@
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
-      <c r="AC91" s="1"/>
+      <c r="AC91" s="1">
+        <v>0</v>
+      </c>
       <c r="AD91" s="1">
         <v>0</v>
       </c>
@@ -5129,7 +5325,9 @@
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
-      <c r="AC92" s="1"/>
+      <c r="AC92" s="1">
+        <v>0</v>
+      </c>
       <c r="AD92" s="1">
         <v>0</v>
       </c>
@@ -5176,7 +5374,9 @@
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
-      <c r="AC93" s="1"/>
+      <c r="AC93" s="1">
+        <v>0</v>
+      </c>
       <c r="AD93" s="1">
         <v>0</v>
       </c>
@@ -5223,7 +5423,9 @@
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
-      <c r="AC94" s="1"/>
+      <c r="AC94" s="1">
+        <v>0</v>
+      </c>
       <c r="AD94" s="1">
         <v>0</v>
       </c>
@@ -5271,7 +5473,9 @@
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
-      <c r="AC95" s="1"/>
+      <c r="AC95" s="1">
+        <v>0</v>
+      </c>
       <c r="AD95" s="1">
         <v>0</v>
       </c>
@@ -5319,7 +5523,9 @@
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
-      <c r="AC96" s="1"/>
+      <c r="AC96" s="1">
+        <v>0</v>
+      </c>
       <c r="AD96" s="1">
         <v>0</v>
       </c>
@@ -5367,7 +5573,9 @@
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
-      <c r="AC97" s="1"/>
+      <c r="AC97" s="1">
+        <v>0</v>
+      </c>
       <c r="AD97" s="1">
         <v>0</v>
       </c>
@@ -5415,7 +5623,9 @@
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
-      <c r="AC98" s="1"/>
+      <c r="AC98" s="1">
+        <v>0</v>
+      </c>
       <c r="AD98" s="1">
         <v>0</v>
       </c>
@@ -5463,7 +5673,9 @@
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
-      <c r="AC99" s="1"/>
+      <c r="AC99" s="1">
+        <v>0</v>
+      </c>
       <c r="AD99" s="1">
         <v>0</v>
       </c>
@@ -5512,7 +5724,9 @@
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
-      <c r="AC100" s="1"/>
+      <c r="AC100" s="1">
+        <v>0</v>
+      </c>
       <c r="AD100" s="1">
         <v>0</v>
       </c>
@@ -5561,7 +5775,9 @@
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
-      <c r="AC101" s="1"/>
+      <c r="AC101" s="1">
+        <v>0</v>
+      </c>
       <c r="AD101" s="1">
         <v>0</v>
       </c>
@@ -5610,7 +5826,9 @@
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
-      <c r="AC102" s="1"/>
+      <c r="AC102" s="1">
+        <v>0</v>
+      </c>
       <c r="AD102" s="1">
         <v>0</v>
       </c>
@@ -5659,7 +5877,9 @@
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
-      <c r="AC103" s="1"/>
+      <c r="AC103" s="1">
+        <v>0</v>
+      </c>
       <c r="AD103" s="1">
         <v>0</v>
       </c>
@@ -5709,7 +5929,9 @@
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
-      <c r="AC104" s="1"/>
+      <c r="AC104" s="1">
+        <v>0</v>
+      </c>
       <c r="AD104" s="1">
         <v>0</v>
       </c>
@@ -5759,7 +5981,9 @@
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
-      <c r="AC105" s="1"/>
+      <c r="AC105" s="1">
+        <v>0</v>
+      </c>
       <c r="AD105" s="1">
         <v>0</v>
       </c>
@@ -5810,7 +6034,9 @@
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
-      <c r="AC106" s="1"/>
+      <c r="AC106" s="1">
+        <v>0</v>
+      </c>
       <c r="AD106" s="1">
         <v>0</v>
       </c>
@@ -5861,7 +6087,9 @@
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
-      <c r="AC107" s="1"/>
+      <c r="AC107" s="1">
+        <v>0</v>
+      </c>
       <c r="AD107" s="1">
         <v>0</v>
       </c>
@@ -5912,7 +6140,9 @@
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
-      <c r="AC108" s="1"/>
+      <c r="AC108" s="1">
+        <v>0</v>
+      </c>
       <c r="AD108" s="1">
         <v>0</v>
       </c>
@@ -5964,7 +6194,9 @@
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
-      <c r="AC109" s="1"/>
+      <c r="AC109" s="1">
+        <v>0</v>
+      </c>
       <c r="AD109" s="1">
         <v>0</v>
       </c>
@@ -6016,7 +6248,9 @@
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
-      <c r="AC110" s="1"/>
+      <c r="AC110" s="1">
+        <v>0</v>
+      </c>
       <c r="AD110" s="1">
         <v>0</v>
       </c>
@@ -6068,7 +6302,9 @@
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
-      <c r="AC111" s="1"/>
+      <c r="AC111" s="1">
+        <v>0</v>
+      </c>
       <c r="AD111" s="1">
         <v>0</v>
       </c>
@@ -6121,7 +6357,9 @@
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
-      <c r="AC112" s="1"/>
+      <c r="AC112" s="1">
+        <v>0</v>
+      </c>
       <c r="AD112" s="1">
         <v>0</v>
       </c>
@@ -6174,7 +6412,9 @@
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
-      <c r="AC113" s="1"/>
+      <c r="AC113" s="1">
+        <v>0</v>
+      </c>
       <c r="AD113" s="1">
         <v>0</v>
       </c>
@@ -6227,7 +6467,9 @@
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
-      <c r="AC114" s="1"/>
+      <c r="AC114" s="1">
+        <v>0</v>
+      </c>
       <c r="AD114" s="1">
         <v>0</v>
       </c>
@@ -6281,7 +6523,9 @@
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
-      <c r="AC115" s="1"/>
+      <c r="AC115" s="1">
+        <v>0</v>
+      </c>
       <c r="AD115" s="1">
         <v>0</v>
       </c>
@@ -6335,7 +6579,9 @@
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
-      <c r="AC116" s="1"/>
+      <c r="AC116" s="1">
+        <v>0</v>
+      </c>
       <c r="AD116" s="1">
         <v>0</v>
       </c>
@@ -6390,7 +6636,9 @@
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
-      <c r="AC117" s="1"/>
+      <c r="AC117" s="1">
+        <v>0</v>
+      </c>
       <c r="AD117" s="1">
         <v>0</v>
       </c>
@@ -6445,7 +6693,9 @@
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
-      <c r="AC118" s="1"/>
+      <c r="AC118" s="1">
+        <v>0</v>
+      </c>
       <c r="AD118" s="1">
         <v>0</v>
       </c>
@@ -6500,7 +6750,9 @@
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
-      <c r="AC119" s="1"/>
+      <c r="AC119" s="1">
+        <v>0</v>
+      </c>
       <c r="AD119" s="1">
         <v>0</v>
       </c>
@@ -6556,7 +6808,9 @@
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
-      <c r="AC120" s="1"/>
+      <c r="AC120" s="1">
+        <v>0</v>
+      </c>
       <c r="AD120" s="1">
         <v>0</v>
       </c>
@@ -6612,7 +6866,9 @@
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
-      <c r="AC121" s="1"/>
+      <c r="AC121" s="1">
+        <v>0</v>
+      </c>
       <c r="AD121" s="1">
         <v>0</v>
       </c>
@@ -6668,7 +6924,9 @@
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
-      <c r="AC122" s="1"/>
+      <c r="AC122" s="1">
+        <v>0</v>
+      </c>
       <c r="AD122" s="1">
         <v>0</v>
       </c>
@@ -6725,7 +6983,9 @@
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
-      <c r="AC123" s="1"/>
+      <c r="AC123" s="1">
+        <v>0</v>
+      </c>
       <c r="AD123" s="1">
         <v>0</v>
       </c>
@@ -6782,7 +7042,9 @@
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
-      <c r="AC124" s="1"/>
+      <c r="AC124" s="1">
+        <v>0</v>
+      </c>
       <c r="AD124" s="1">
         <v>0</v>
       </c>
@@ -6839,7 +7101,9 @@
       <c r="Z125" s="1"/>
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
-      <c r="AC125" s="1"/>
+      <c r="AC125" s="1">
+        <v>0</v>
+      </c>
       <c r="AD125" s="1">
         <v>0</v>
       </c>
@@ -6897,7 +7161,9 @@
       <c r="Z126" s="1"/>
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
-      <c r="AC126" s="1"/>
+      <c r="AC126" s="1">
+        <v>0</v>
+      </c>
       <c r="AD126" s="1">
         <v>0</v>
       </c>
@@ -7972,11 +8238,1151 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B19" si="0">SUM(C3:S3)</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
         <v>0</v>
       </c>
     </row>

--- a/Data_Files/Driver_Wins.xlsx
+++ b/Data_Files/Driver_Wins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0597C2-6571-441D-892F-CA87B515ADF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0671169E-849F-41FC-9E4E-F8630DE0E17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Wins" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1017,9 +1017,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1084,13 +1085,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1133,13 +1134,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1601,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL126"/>
+  <dimension ref="A1:AL124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -1725,6 +1726,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
       <c r="AC2">
         <v>9</v>
       </c>
@@ -1760,6 +1764,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
       <c r="AC3">
         <v>1</v>
       </c>
@@ -1795,6 +1802,9 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
       <c r="AC4" s="1">
         <v>0</v>
       </c>
@@ -1830,6 +1840,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
       <c r="AC5">
         <v>3</v>
       </c>
@@ -1865,6 +1878,9 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
       <c r="AC6" s="1">
         <v>0</v>
       </c>
@@ -1900,6 +1916,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AB7">
+        <v>3</v>
+      </c>
       <c r="AC7">
         <v>0</v>
       </c>
@@ -1935,7 +1954,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="AB8" s="1"/>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
       <c r="AC8" s="1">
         <v>0</v>
       </c>
@@ -1971,6 +1992,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
       <c r="AC9">
         <v>0</v>
       </c>
@@ -2006,6 +2030,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
       <c r="AC10">
         <v>0</v>
       </c>
@@ -2041,6 +2068,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
       <c r="AC11">
         <v>0</v>
       </c>
@@ -2076,6 +2106,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
       <c r="AC12">
         <v>0</v>
       </c>
@@ -2111,6 +2144,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
       <c r="AC13">
         <v>0</v>
       </c>
@@ -2143,7 +2179,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="AB14" s="1"/>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
       <c r="AC14" s="1">
         <v>0</v>
       </c>
@@ -2179,6 +2217,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
       <c r="AC15">
         <v>0</v>
       </c>
@@ -2214,6 +2255,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
       <c r="AC16">
         <v>0</v>
       </c>
@@ -2249,6 +2293,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
       <c r="AC17">
         <v>0</v>
       </c>
@@ -2281,7 +2328,9 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="1"/>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
       <c r="AC18" s="1">
         <v>0</v>
       </c>
@@ -2317,7 +2366,9 @@
       <c r="A19" t="s">
         <v>85</v>
       </c>
-      <c r="AB19" s="1"/>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
       <c r="AC19" s="1">
         <v>0</v>
       </c>
@@ -2353,6 +2404,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
@@ -2388,6 +2442,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
       <c r="AC21" s="1">
         <v>0</v>
       </c>
@@ -2423,6 +2480,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
       <c r="AC22">
         <v>0</v>
       </c>
@@ -2458,6 +2518,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
       <c r="AC23">
         <v>0</v>
       </c>
@@ -2493,7 +2556,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="AB24" s="1"/>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
@@ -2529,6 +2594,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
       <c r="AC25" s="1">
         <v>0</v>
       </c>
@@ -2565,7 +2633,9 @@
         <v>45</v>
       </c>
       <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
+      <c r="AB26" s="1">
+        <v>0</v>
+      </c>
       <c r="AC26" s="1">
         <v>0</v>
       </c>
@@ -2602,7 +2672,9 @@
         <v>46</v>
       </c>
       <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
+      <c r="AB27" s="1">
+        <v>0</v>
+      </c>
       <c r="AC27" s="1">
         <v>0</v>
       </c>
@@ -2638,6 +2710,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
       <c r="AC28">
         <v>0</v>
       </c>
@@ -2674,7 +2749,9 @@
         <v>48</v>
       </c>
       <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
+      <c r="AB29" s="1">
+        <v>0</v>
+      </c>
       <c r="AC29" s="1">
         <v>0</v>
       </c>
@@ -2711,7 +2788,9 @@
         <v>49</v>
       </c>
       <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
+      <c r="AB30" s="1">
+        <v>0</v>
+      </c>
       <c r="AC30" s="1">
         <v>0</v>
       </c>
@@ -2745,12 +2824,15 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
+        <v>53</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
         <v>0</v>
       </c>
       <c r="AE31" s="1">
@@ -2780,10 +2862,12 @@
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
+      <c r="AB32" s="1">
+        <v>0</v>
+      </c>
       <c r="AC32" s="1">
         <v>0</v>
       </c>
@@ -2817,12 +2901,16 @@
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
+        <v>58</v>
+      </c>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="1">
         <v>0</v>
       </c>
       <c r="AE33" s="1">
@@ -2852,10 +2940,12 @@
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
@@ -2889,10 +2979,12 @@
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
+      <c r="AB35" s="1">
+        <v>0</v>
+      </c>
       <c r="AC35" s="1">
         <v>0</v>
       </c>
@@ -2926,10 +3018,12 @@
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
+      <c r="AB36" s="1">
+        <v>0</v>
+      </c>
       <c r="AC36" s="1">
         <v>0</v>
       </c>
@@ -2963,10 +3057,13 @@
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
+      <c r="AB37" s="1">
+        <v>0</v>
+      </c>
       <c r="AC37" s="1">
         <v>0</v>
       </c>
@@ -3000,10 +3097,13 @@
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
       <c r="AC38" s="1">
         <v>0</v>
       </c>
@@ -3037,15 +3137,12 @@
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="1">
+        <v>64</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
         <v>0</v>
       </c>
       <c r="AE39" s="1">
@@ -3075,11 +3172,13 @@
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
+      <c r="AB40" s="1">
+        <v>0</v>
+      </c>
       <c r="AC40" s="1">
         <v>0</v>
       </c>
@@ -3113,9 +3212,17 @@
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC41">
+        <v>66</v>
+      </c>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
         <v>0</v>
       </c>
       <c r="AE41" s="1">
@@ -3145,11 +3252,14 @@
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>65</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
+      <c r="AB42" s="1">
+        <v>0</v>
+      </c>
       <c r="AC42" s="1">
         <v>0</v>
       </c>
@@ -3183,21 +3293,18 @@
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="1">
+        <v>68</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
         <v>0</v>
       </c>
       <c r="AG43" s="1">
@@ -3221,12 +3328,14 @@
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
+      <c r="AB44" s="1">
+        <v>0</v>
+      </c>
       <c r="AC44" s="1">
         <v>0</v>
       </c>
@@ -3260,15 +3369,24 @@
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AE45">
-        <v>0</v>
-      </c>
-      <c r="AF45">
+        <v>70</v>
+      </c>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="1">
         <v>0</v>
       </c>
       <c r="AG45" s="1">
@@ -3292,12 +3410,14 @@
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
+      <c r="AB46" s="1">
+        <v>0</v>
+      </c>
       <c r="AC46" s="1">
         <v>0</v>
       </c>
@@ -3331,12 +3451,14 @@
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
-      <c r="AB47" s="1"/>
+      <c r="AB47" s="1">
+        <v>0</v>
+      </c>
       <c r="AC47" s="1">
         <v>0</v>
       </c>
@@ -3370,12 +3492,14 @@
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
-      <c r="AB48" s="1"/>
+      <c r="AB48" s="1">
+        <v>0</v>
+      </c>
       <c r="AC48" s="1">
         <v>0</v>
       </c>
@@ -3409,12 +3533,15 @@
     </row>
     <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>72</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
-      <c r="AB49" s="1"/>
+      <c r="AB49" s="1">
+        <v>0</v>
+      </c>
       <c r="AC49" s="1">
         <v>0</v>
       </c>
@@ -3448,12 +3575,15 @@
     </row>
     <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
-      <c r="AB50" s="1"/>
+      <c r="AB50" s="1">
+        <v>0</v>
+      </c>
       <c r="AC50" s="1">
         <v>0</v>
       </c>
@@ -3487,13 +3617,15 @@
     </row>
     <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
-      <c r="AB51" s="1"/>
+      <c r="AB51" s="1">
+        <v>0</v>
+      </c>
       <c r="AC51" s="1">
         <v>0</v>
       </c>
@@ -3527,13 +3659,15 @@
     </row>
     <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
+      <c r="AB52" s="1">
+        <v>0</v>
+      </c>
       <c r="AC52" s="1">
         <v>0</v>
       </c>
@@ -3567,13 +3701,15 @@
     </row>
     <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
-      <c r="AB53" s="1"/>
+      <c r="AB53" s="1">
+        <v>0</v>
+      </c>
       <c r="AC53" s="1">
         <v>0</v>
       </c>
@@ -3607,13 +3743,15 @@
     </row>
     <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
+      <c r="AB54" s="1">
+        <v>0</v>
+      </c>
       <c r="AC54" s="1">
         <v>0</v>
       </c>
@@ -3647,13 +3785,16 @@
     </row>
     <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>78</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
-      <c r="AB55" s="1"/>
+      <c r="AB55" s="1">
+        <v>0</v>
+      </c>
       <c r="AC55" s="1">
         <v>0</v>
       </c>
@@ -3687,13 +3828,16 @@
     </row>
     <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>79</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
+      <c r="AB56" s="1">
+        <v>0</v>
+      </c>
       <c r="AC56" s="1">
         <v>0</v>
       </c>
@@ -3727,14 +3871,16 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
-      <c r="AB57" s="1"/>
+      <c r="AB57" s="1">
+        <v>0</v>
+      </c>
       <c r="AC57" s="1">
         <v>0</v>
       </c>
@@ -3768,14 +3914,16 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
+      <c r="AB58" s="1">
+        <v>0</v>
+      </c>
       <c r="AC58" s="1">
         <v>0</v>
       </c>
@@ -3809,14 +3957,16 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
-      <c r="AB59" s="1"/>
+      <c r="AB59" s="1">
+        <v>0</v>
+      </c>
       <c r="AC59" s="1">
         <v>0</v>
       </c>
@@ -3850,14 +4000,17 @@
     </row>
     <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>83</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
-      <c r="AB60" s="1"/>
+      <c r="AB60" s="1">
+        <v>0</v>
+      </c>
       <c r="AC60" s="1">
         <v>0</v>
       </c>
@@ -3891,14 +4044,17 @@
     </row>
     <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
-      <c r="AB61" s="1"/>
+      <c r="AB61" s="1">
+        <v>0</v>
+      </c>
       <c r="AC61" s="1">
         <v>0</v>
       </c>
@@ -3932,15 +4088,18 @@
     </row>
     <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>86</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
-      <c r="AB62" s="1"/>
+      <c r="AB62" s="1">
+        <v>0</v>
+      </c>
       <c r="AC62" s="1">
         <v>0</v>
       </c>
@@ -3974,15 +4133,18 @@
     </row>
     <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>87</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
-      <c r="AB63" s="1"/>
+      <c r="AB63" s="1">
+        <v>0</v>
+      </c>
       <c r="AC63" s="1">
         <v>0</v>
       </c>
@@ -4016,7 +4178,7 @@
     </row>
     <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
@@ -4025,7 +4187,9 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
-      <c r="AB64" s="1"/>
+      <c r="AB64" s="1">
+        <v>0</v>
+      </c>
       <c r="AC64" s="1">
         <v>0</v>
       </c>
@@ -4059,7 +4223,7 @@
     </row>
     <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
@@ -4068,7 +4232,9 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
-      <c r="AB65" s="1"/>
+      <c r="AB65" s="1">
+        <v>0</v>
+      </c>
       <c r="AC65" s="1">
         <v>0</v>
       </c>
@@ -4102,38 +4268,54 @@
     </row>
     <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>90</v>
-      </c>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
-      <c r="AB66" s="1"/>
-      <c r="AC66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ66" s="1">
+        <v>92</v>
+      </c>
+      <c r="U66" s="2">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2">
+        <v>0</v>
+      </c>
+      <c r="W66" s="2">
+        <v>0</v>
+      </c>
+      <c r="X66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="2">
         <v>0</v>
       </c>
       <c r="AK66" s="1">
@@ -4145,8 +4327,9 @@
     </row>
     <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>91</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
@@ -4154,7 +4337,9 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
-      <c r="AB67" s="1"/>
+      <c r="AB67" s="1">
+        <v>0</v>
+      </c>
       <c r="AC67" s="1">
         <v>0</v>
       </c>
@@ -4188,36 +4373,23 @@
     </row>
     <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>92</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="1">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="1">
-        <v>0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
       <c r="AB68" s="1">
         <v>0</v>
       </c>
       <c r="AC68" s="1">
         <v>0</v>
       </c>
-      <c r="AD68">
+      <c r="AD68" s="1">
         <v>0</v>
       </c>
       <c r="AE68" s="1">
@@ -4226,16 +4398,16 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68">
+      <c r="AG68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="1">
         <v>0</v>
       </c>
       <c r="AI68" s="1">
         <v>0</v>
       </c>
-      <c r="AJ68">
+      <c r="AJ68" s="1">
         <v>0</v>
       </c>
       <c r="AK68" s="1">
@@ -4247,7 +4419,7 @@
     </row>
     <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
@@ -4257,7 +4429,9 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
-      <c r="AB69" s="1"/>
+      <c r="AB69" s="1">
+        <v>0</v>
+      </c>
       <c r="AC69" s="1">
         <v>0</v>
       </c>
@@ -4291,7 +4465,7 @@
     </row>
     <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
@@ -4301,7 +4475,9 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
-      <c r="AB70" s="1"/>
+      <c r="AB70" s="1">
+        <v>0</v>
+      </c>
       <c r="AC70" s="1">
         <v>0</v>
       </c>
@@ -4335,7 +4511,7 @@
     </row>
     <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
@@ -4345,7 +4521,9 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
-      <c r="AB71" s="1"/>
+      <c r="AB71" s="1">
+        <v>0</v>
+      </c>
       <c r="AC71" s="1">
         <v>0</v>
       </c>
@@ -4379,8 +4557,9 @@
     </row>
     <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>96</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="S72" s="1"/>
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
@@ -4389,7 +4568,9 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
-      <c r="AB72" s="1"/>
+      <c r="AB72" s="1">
+        <v>0</v>
+      </c>
       <c r="AC72" s="1">
         <v>0</v>
       </c>
@@ -4423,8 +4604,9 @@
     </row>
     <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>97</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
@@ -4433,7 +4615,9 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
-      <c r="AB73" s="1"/>
+      <c r="AB73" s="1">
+        <v>0</v>
+      </c>
       <c r="AC73" s="1">
         <v>0</v>
       </c>
@@ -4467,7 +4651,7 @@
     </row>
     <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
@@ -4478,7 +4662,9 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
-      <c r="AB74" s="1"/>
+      <c r="AB74" s="1">
+        <v>0</v>
+      </c>
       <c r="AC74" s="1">
         <v>0</v>
       </c>
@@ -4512,7 +4698,7 @@
     </row>
     <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
@@ -4523,7 +4709,9 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
-      <c r="AB75" s="1"/>
+      <c r="AB75" s="1">
+        <v>0</v>
+      </c>
       <c r="AC75" s="1">
         <v>0</v>
       </c>
@@ -4557,7 +4745,7 @@
     </row>
     <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
@@ -4568,7 +4756,9 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
-      <c r="AB76" s="1"/>
+      <c r="AB76" s="1">
+        <v>0</v>
+      </c>
       <c r="AC76" s="1">
         <v>0</v>
       </c>
@@ -4602,8 +4792,9 @@
     </row>
     <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>101</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -4613,7 +4804,9 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
-      <c r="AB77" s="1"/>
+      <c r="AB77" s="1">
+        <v>0</v>
+      </c>
       <c r="AC77" s="1">
         <v>0</v>
       </c>
@@ -4647,8 +4840,9 @@
     </row>
     <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>102</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -4658,7 +4852,9 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
-      <c r="AB78" s="1"/>
+      <c r="AB78" s="1">
+        <v>0</v>
+      </c>
       <c r="AC78" s="1">
         <v>0</v>
       </c>
@@ -4692,8 +4888,9 @@
     </row>
     <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>103</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
@@ -4704,7 +4901,9 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
-      <c r="AB79" s="1"/>
+      <c r="AB79" s="1">
+        <v>0</v>
+      </c>
       <c r="AC79" s="1">
         <v>0</v>
       </c>
@@ -4738,8 +4937,9 @@
     </row>
     <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>104</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
@@ -4750,7 +4950,9 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
-      <c r="AB80" s="1"/>
+      <c r="AB80" s="1">
+        <v>0</v>
+      </c>
       <c r="AC80" s="1">
         <v>0</v>
       </c>
@@ -4784,7 +4986,7 @@
     </row>
     <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
@@ -4797,7 +4999,9 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
-      <c r="AB81" s="1"/>
+      <c r="AB81" s="1">
+        <v>0</v>
+      </c>
       <c r="AC81" s="1">
         <v>0</v>
       </c>
@@ -4831,7 +5035,7 @@
     </row>
     <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
@@ -4844,7 +5048,9 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
-      <c r="AB82" s="1"/>
+      <c r="AB82" s="1">
+        <v>0</v>
+      </c>
       <c r="AC82" s="1">
         <v>0</v>
       </c>
@@ -4878,7 +5084,7 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
@@ -4891,7 +5097,9 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
-      <c r="AB83" s="1"/>
+      <c r="AB83" s="1">
+        <v>0</v>
+      </c>
       <c r="AC83" s="1">
         <v>0</v>
       </c>
@@ -4925,8 +5133,9 @@
     </row>
     <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>108</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -4938,7 +5147,9 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
-      <c r="AB84" s="1"/>
+      <c r="AB84" s="1">
+        <v>0</v>
+      </c>
       <c r="AC84" s="1">
         <v>0</v>
       </c>
@@ -4972,8 +5183,9 @@
     </row>
     <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>109</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -4985,7 +5197,9 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
-      <c r="AB85" s="1"/>
+      <c r="AB85" s="1">
+        <v>0</v>
+      </c>
       <c r="AC85" s="1">
         <v>0</v>
       </c>
@@ -5019,7 +5233,7 @@
     </row>
     <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
@@ -5033,7 +5247,9 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
-      <c r="AB86" s="1"/>
+      <c r="AB86" s="1">
+        <v>0</v>
+      </c>
       <c r="AC86" s="1">
         <v>0</v>
       </c>
@@ -5067,7 +5283,7 @@
     </row>
     <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
@@ -5081,7 +5297,9 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
-      <c r="AB87" s="1"/>
+      <c r="AB87" s="1">
+        <v>0</v>
+      </c>
       <c r="AC87" s="1">
         <v>0</v>
       </c>
@@ -5115,8 +5333,9 @@
     </row>
     <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>112</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
@@ -5129,7 +5348,9 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
-      <c r="AB88" s="1"/>
+      <c r="AB88" s="1">
+        <v>0</v>
+      </c>
       <c r="AC88" s="1">
         <v>0</v>
       </c>
@@ -5163,8 +5384,9 @@
     </row>
     <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
@@ -5177,7 +5399,9 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
-      <c r="AB89" s="1"/>
+      <c r="AB89" s="1">
+        <v>0</v>
+      </c>
       <c r="AC89" s="1">
         <v>0</v>
       </c>
@@ -5211,7 +5435,7 @@
     </row>
     <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
@@ -5226,7 +5450,9 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
-      <c r="AB90" s="1"/>
+      <c r="AB90" s="1">
+        <v>0</v>
+      </c>
       <c r="AC90" s="1">
         <v>0</v>
       </c>
@@ -5260,7 +5486,7 @@
     </row>
     <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
@@ -5275,7 +5501,9 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
-      <c r="AB91" s="1"/>
+      <c r="AB91" s="1">
+        <v>0</v>
+      </c>
       <c r="AC91" s="1">
         <v>0</v>
       </c>
@@ -5309,7 +5537,7 @@
     </row>
     <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
@@ -5324,7 +5552,9 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
-      <c r="AB92" s="1"/>
+      <c r="AB92" s="1">
+        <v>0</v>
+      </c>
       <c r="AC92" s="1">
         <v>0</v>
       </c>
@@ -5358,8 +5588,9 @@
     </row>
     <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>117</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
@@ -5373,7 +5604,9 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
-      <c r="AB93" s="1"/>
+      <c r="AB93" s="1">
+        <v>0</v>
+      </c>
       <c r="AC93" s="1">
         <v>0</v>
       </c>
@@ -5407,8 +5640,9 @@
     </row>
     <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>118</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N94" s="1"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
@@ -5422,7 +5656,9 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
-      <c r="AB94" s="1"/>
+      <c r="AB94" s="1">
+        <v>0</v>
+      </c>
       <c r="AC94" s="1">
         <v>0</v>
       </c>
@@ -5456,7 +5692,7 @@
     </row>
     <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
@@ -5472,7 +5708,9 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
-      <c r="AB95" s="1"/>
+      <c r="AB95" s="1">
+        <v>0</v>
+      </c>
       <c r="AC95" s="1">
         <v>0</v>
       </c>
@@ -5506,7 +5744,7 @@
     </row>
     <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
@@ -5522,7 +5760,9 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
-      <c r="AB96" s="1"/>
+      <c r="AB96" s="1">
+        <v>0</v>
+      </c>
       <c r="AC96" s="1">
         <v>0</v>
       </c>
@@ -5556,7 +5796,7 @@
     </row>
     <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
@@ -5572,7 +5812,9 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
-      <c r="AB97" s="1"/>
+      <c r="AB97" s="1">
+        <v>0</v>
+      </c>
       <c r="AC97" s="1">
         <v>0</v>
       </c>
@@ -5606,8 +5848,9 @@
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
@@ -5622,7 +5865,9 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
-      <c r="AB98" s="1"/>
+      <c r="AB98" s="1">
+        <v>0</v>
+      </c>
       <c r="AC98" s="1">
         <v>0</v>
       </c>
@@ -5656,8 +5901,9 @@
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>123</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
@@ -5672,7 +5918,9 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
-      <c r="AB99" s="1"/>
+      <c r="AB99" s="1">
+        <v>0</v>
+      </c>
       <c r="AC99" s="1">
         <v>0</v>
       </c>
@@ -5706,7 +5954,7 @@
     </row>
     <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
@@ -5723,7 +5971,9 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
-      <c r="AB100" s="1"/>
+      <c r="AB100" s="1">
+        <v>0</v>
+      </c>
       <c r="AC100" s="1">
         <v>0</v>
       </c>
@@ -5757,7 +6007,7 @@
     </row>
     <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -5774,7 +6024,9 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
-      <c r="AB101" s="1"/>
+      <c r="AB101" s="1">
+        <v>0</v>
+      </c>
       <c r="AC101" s="1">
         <v>0</v>
       </c>
@@ -5808,8 +6060,9 @@
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>126</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
@@ -5825,7 +6078,9 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
-      <c r="AB102" s="1"/>
+      <c r="AB102" s="1">
+        <v>0</v>
+      </c>
       <c r="AC102" s="1">
         <v>0</v>
       </c>
@@ -5859,8 +6114,9 @@
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>127</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
@@ -5876,7 +6132,9 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
-      <c r="AB103" s="1"/>
+      <c r="AB103" s="1">
+        <v>0</v>
+      </c>
       <c r="AC103" s="1">
         <v>0</v>
       </c>
@@ -5910,8 +6168,9 @@
     </row>
     <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>128</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -5928,7 +6187,9 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
-      <c r="AB104" s="1"/>
+      <c r="AB104" s="1">
+        <v>0</v>
+      </c>
       <c r="AC104" s="1">
         <v>0</v>
       </c>
@@ -5962,8 +6223,9 @@
     </row>
     <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>129</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -5980,7 +6242,9 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
-      <c r="AB105" s="1"/>
+      <c r="AB105" s="1">
+        <v>0</v>
+      </c>
       <c r="AC105" s="1">
         <v>0</v>
       </c>
@@ -6014,7 +6278,7 @@
     </row>
     <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6033,7 +6297,9 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
-      <c r="AB106" s="1"/>
+      <c r="AB106" s="1">
+        <v>0</v>
+      </c>
       <c r="AC106" s="1">
         <v>0</v>
       </c>
@@ -6067,8 +6333,9 @@
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>131</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
@@ -6086,7 +6353,9 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
-      <c r="AB107" s="1"/>
+      <c r="AB107" s="1">
+        <v>0</v>
+      </c>
       <c r="AC107" s="1">
         <v>0</v>
       </c>
@@ -6120,8 +6389,9 @@
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
@@ -6139,7 +6409,9 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
+      <c r="AB108" s="1">
+        <v>0</v>
+      </c>
       <c r="AC108" s="1">
         <v>0</v>
       </c>
@@ -6173,7 +6445,7 @@
     </row>
     <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
@@ -6193,7 +6465,9 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
-      <c r="AB109" s="1"/>
+      <c r="AB109" s="1">
+        <v>0</v>
+      </c>
       <c r="AC109" s="1">
         <v>0</v>
       </c>
@@ -6227,8 +6501,9 @@
     </row>
     <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>134</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -6247,7 +6522,9 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
-      <c r="AB110" s="1"/>
+      <c r="AB110" s="1">
+        <v>0</v>
+      </c>
       <c r="AC110" s="1">
         <v>0</v>
       </c>
@@ -6281,8 +6558,9 @@
     </row>
     <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>135</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -6301,7 +6579,9 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
-      <c r="AB111" s="1"/>
+      <c r="AB111" s="1">
+        <v>0</v>
+      </c>
       <c r="AC111" s="1">
         <v>0</v>
       </c>
@@ -6335,7 +6615,7 @@
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6356,7 +6636,9 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
-      <c r="AB112" s="1"/>
+      <c r="AB112" s="1">
+        <v>0</v>
+      </c>
       <c r="AC112" s="1">
         <v>0</v>
       </c>
@@ -6390,8 +6672,9 @@
     </row>
     <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>137</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -6411,7 +6694,9 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
-      <c r="AB113" s="1"/>
+      <c r="AB113" s="1">
+        <v>0</v>
+      </c>
       <c r="AC113" s="1">
         <v>0</v>
       </c>
@@ -6445,8 +6730,9 @@
     </row>
     <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>138</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
@@ -6466,7 +6752,9 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
-      <c r="AB114" s="1"/>
+      <c r="AB114" s="1">
+        <v>0</v>
+      </c>
       <c r="AC114" s="1">
         <v>0</v>
       </c>
@@ -6500,8 +6788,9 @@
     </row>
     <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>139</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6522,7 +6811,9 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
-      <c r="AB115" s="1"/>
+      <c r="AB115" s="1">
+        <v>0</v>
+      </c>
       <c r="AC115" s="1">
         <v>0</v>
       </c>
@@ -6556,8 +6847,9 @@
     </row>
     <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6578,7 +6870,9 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
-      <c r="AB116" s="1"/>
+      <c r="AB116" s="1">
+        <v>0</v>
+      </c>
       <c r="AC116" s="1">
         <v>0</v>
       </c>
@@ -6612,7 +6906,7 @@
     </row>
     <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
@@ -6635,7 +6929,9 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
-      <c r="AB117" s="1"/>
+      <c r="AB117" s="1">
+        <v>0</v>
+      </c>
       <c r="AC117" s="1">
         <v>0</v>
       </c>
@@ -6669,8 +6965,9 @@
     </row>
     <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>142</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -6692,7 +6989,9 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
-      <c r="AB118" s="1"/>
+      <c r="AB118" s="1">
+        <v>0</v>
+      </c>
       <c r="AC118" s="1">
         <v>0</v>
       </c>
@@ -6726,8 +7025,9 @@
     </row>
     <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -6749,7 +7049,9 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
-      <c r="AB119" s="1"/>
+      <c r="AB119" s="1">
+        <v>0</v>
+      </c>
       <c r="AC119" s="1">
         <v>0</v>
       </c>
@@ -6783,7 +7085,7 @@
     </row>
     <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
@@ -6807,7 +7109,9 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
-      <c r="AB120" s="1"/>
+      <c r="AB120" s="1">
+        <v>0</v>
+      </c>
       <c r="AC120" s="1">
         <v>0</v>
       </c>
@@ -6841,8 +7145,9 @@
     </row>
     <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>145</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -6865,7 +7170,9 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
-      <c r="AB121" s="1"/>
+      <c r="AB121" s="1">
+        <v>0</v>
+      </c>
       <c r="AC121" s="1">
         <v>0</v>
       </c>
@@ -6899,8 +7206,9 @@
     </row>
     <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>146</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -6923,7 +7231,9 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
-      <c r="AB122" s="1"/>
+      <c r="AB122" s="1">
+        <v>0</v>
+      </c>
       <c r="AC122" s="1">
         <v>0</v>
       </c>
@@ -6957,7 +7267,7 @@
     </row>
     <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -6982,7 +7292,9 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
-      <c r="AB123" s="1"/>
+      <c r="AB123" s="1">
+        <v>0</v>
+      </c>
       <c r="AC123" s="1">
         <v>0</v>
       </c>
@@ -7016,8 +7328,9 @@
     </row>
     <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>148</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -7041,7 +7354,9 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
-      <c r="AB124" s="1"/>
+      <c r="AB124" s="1">
+        <v>0</v>
+      </c>
       <c r="AC124" s="1">
         <v>0</v>
       </c>
@@ -7070,125 +7385,6 @@
         <v>0</v>
       </c>
       <c r="AL124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>149</v>
-      </c>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="1"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
-      <c r="U125" s="1"/>
-      <c r="V125" s="1"/>
-      <c r="W125" s="1"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="1"/>
-      <c r="Z125" s="1"/>
-      <c r="AA125" s="1"/>
-      <c r="AB125" s="1"/>
-      <c r="AC125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>150</v>
-      </c>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
-      <c r="U126" s="1"/>
-      <c r="V126" s="1"/>
-      <c r="W126" s="1"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="1"/>
-      <c r="Z126" s="1"/>
-      <c r="AA126" s="1"/>
-      <c r="AB126" s="1"/>
-      <c r="AC126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL126" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9393,11 +9589,1269 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
         <v>0</v>
       </c>
     </row>

--- a/Data_Files/Driver_Wins.xlsx
+++ b/Data_Files/Driver_Wins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0671169E-849F-41FC-9E4E-F8630DE0E17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D424367-A558-4430-B1E5-13DDB5A3378F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" firstSheet="6" activeTab="13" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Wins" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1017,10 +1017,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1726,6 +1725,12 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="Z2">
+        <v>6</v>
+      </c>
+      <c r="AA2">
+        <v>11</v>
+      </c>
       <c r="AB2">
         <v>9</v>
       </c>
@@ -1764,6 +1769,12 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="Z3">
+        <v>2</v>
+      </c>
+      <c r="AA3">
+        <v>4</v>
+      </c>
       <c r="AB3">
         <v>0</v>
       </c>
@@ -1802,6 +1813,12 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
       <c r="AB4">
         <v>0</v>
       </c>
@@ -1840,6 +1857,12 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
       <c r="AB5">
         <v>2</v>
       </c>
@@ -1878,6 +1901,12 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
       <c r="AB6">
         <v>1</v>
       </c>
@@ -1916,6 +1945,12 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="Z7">
+        <v>2</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
       <c r="AB7">
         <v>3</v>
       </c>
@@ -1954,6 +1989,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
@@ -1992,6 +2030,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
       <c r="AB9">
         <v>0</v>
       </c>
@@ -2030,6 +2071,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
       <c r="AB10">
         <v>0</v>
       </c>
@@ -2068,6 +2112,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
       <c r="AB11">
         <v>0</v>
       </c>
@@ -2106,6 +2153,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
       <c r="AB12">
         <v>0</v>
       </c>
@@ -2144,6 +2194,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
       <c r="AB13">
         <v>0</v>
       </c>
@@ -2179,6 +2232,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
       <c r="AB14" s="1">
         <v>0</v>
       </c>
@@ -2217,6 +2273,12 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
       <c r="AB15">
         <v>0</v>
       </c>
@@ -2255,6 +2317,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
       <c r="AB16">
         <v>0</v>
       </c>
@@ -2293,6 +2358,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
       <c r="AB17">
         <v>0</v>
       </c>
@@ -2328,6 +2396,9 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
       <c r="AB18" s="1">
         <v>0</v>
       </c>
@@ -2366,6 +2437,9 @@
       <c r="A19" t="s">
         <v>85</v>
       </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
       <c r="AB19" s="1">
         <v>0</v>
       </c>
@@ -2404,6 +2478,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
       <c r="AB20">
         <v>0</v>
       </c>
@@ -2442,6 +2519,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
       <c r="AB21">
         <v>0</v>
       </c>
@@ -2480,6 +2560,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
       <c r="AB22">
         <v>0</v>
       </c>
@@ -2518,6 +2601,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
       <c r="AB23">
         <v>0</v>
       </c>
@@ -2556,6 +2642,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
       <c r="AB24" s="1">
         <v>0</v>
       </c>
@@ -2594,6 +2683,12 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
       <c r="AB25">
         <v>0</v>
       </c>
@@ -2632,7 +2727,9 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="AA26" s="1"/>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
       <c r="AB26" s="1">
         <v>0</v>
       </c>
@@ -2671,7 +2768,9 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
-      <c r="AA27" s="1"/>
+      <c r="AA27" s="1">
+        <v>0</v>
+      </c>
       <c r="AB27" s="1">
         <v>0</v>
       </c>
@@ -2710,6 +2809,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
       <c r="AB28">
         <v>0</v>
       </c>
@@ -2748,7 +2850,9 @@
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="AA29" s="1"/>
+      <c r="AA29" s="1">
+        <v>0</v>
+      </c>
       <c r="AB29" s="1">
         <v>0</v>
       </c>
@@ -2787,7 +2891,9 @@
       <c r="A30" t="s">
         <v>49</v>
       </c>
-      <c r="AA30" s="1"/>
+      <c r="AA30" s="1">
+        <v>0</v>
+      </c>
       <c r="AB30" s="1">
         <v>0</v>
       </c>
@@ -2826,6 +2932,9 @@
       <c r="A31" t="s">
         <v>53</v>
       </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
       <c r="AB31">
         <v>0</v>
       </c>
@@ -2864,7 +2973,9 @@
       <c r="A32" t="s">
         <v>57</v>
       </c>
-      <c r="AA32" s="1"/>
+      <c r="AA32" s="1">
+        <v>0</v>
+      </c>
       <c r="AB32" s="1">
         <v>0</v>
       </c>
@@ -2903,7 +3014,9 @@
       <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="AA33" s="1"/>
+      <c r="AA33" s="1">
+        <v>0</v>
+      </c>
       <c r="AB33" s="1">
         <v>0</v>
       </c>
@@ -2942,7 +3055,9 @@
       <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="AA34" s="1"/>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
       <c r="AB34" s="1">
         <v>0</v>
       </c>
@@ -2981,7 +3096,9 @@
       <c r="A35" t="s">
         <v>60</v>
       </c>
-      <c r="AA35" s="1"/>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
@@ -3020,7 +3137,9 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" s="1"/>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
       <c r="AB36" s="1">
         <v>0</v>
       </c>
@@ -3060,7 +3179,9 @@
         <v>62</v>
       </c>
       <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
       <c r="AB37" s="1">
         <v>0</v>
       </c>
@@ -3100,7 +3221,9 @@
         <v>63</v>
       </c>
       <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
@@ -3139,6 +3262,9 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
       <c r="AB39">
         <v>0</v>
       </c>
@@ -3175,7 +3301,9 @@
         <v>65</v>
       </c>
       <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
+      <c r="AA40" s="1">
+        <v>0</v>
+      </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
@@ -3215,7 +3343,9 @@
         <v>66</v>
       </c>
       <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
       <c r="AB41" s="1">
         <v>0</v>
       </c>
@@ -3256,7 +3386,9 @@
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
       <c r="AB42" s="1">
         <v>0</v>
       </c>
@@ -3295,6 +3427,9 @@
       <c r="A43" t="s">
         <v>68</v>
       </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
       <c r="AB43">
         <v>0</v>
       </c>
@@ -3332,7 +3467,9 @@
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
@@ -3373,7 +3510,9 @@
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
       <c r="AB45" s="1">
         <v>0</v>
       </c>
@@ -3414,7 +3553,9 @@
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
+      <c r="AA46" s="1">
+        <v>0</v>
+      </c>
       <c r="AB46" s="1">
         <v>0</v>
       </c>
@@ -3455,7 +3596,9 @@
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
+      <c r="AA47" s="1">
+        <v>0</v>
+      </c>
       <c r="AB47" s="1">
         <v>0</v>
       </c>
@@ -3496,7 +3639,9 @@
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="AA48" s="1">
+        <v>0</v>
+      </c>
       <c r="AB48" s="1">
         <v>0</v>
       </c>
@@ -3538,7 +3683,9 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
+      <c r="AA49" s="1">
+        <v>0</v>
+      </c>
       <c r="AB49" s="1">
         <v>0</v>
       </c>
@@ -3580,7 +3727,9 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
       <c r="AB50" s="1">
         <v>0</v>
       </c>
@@ -3622,7 +3771,9 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1">
+        <v>0</v>
+      </c>
       <c r="AB51" s="1">
         <v>0</v>
       </c>
@@ -3664,7 +3815,9 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
       <c r="AB52" s="1">
         <v>0</v>
       </c>
@@ -3706,7 +3859,9 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
       <c r="AB53" s="1">
         <v>0</v>
       </c>
@@ -3748,7 +3903,9 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
+      <c r="AA54" s="1">
+        <v>0</v>
+      </c>
       <c r="AB54" s="1">
         <v>0</v>
       </c>
@@ -3791,7 +3948,9 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
       <c r="AB55" s="1">
         <v>0</v>
       </c>
@@ -3834,7 +3993,9 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
+      <c r="AA56" s="1">
+        <v>0</v>
+      </c>
       <c r="AB56" s="1">
         <v>0</v>
       </c>
@@ -3877,7 +4038,9 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
       <c r="AB57" s="1">
         <v>0</v>
       </c>
@@ -3920,7 +4083,9 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
+      <c r="AA58" s="1">
+        <v>0</v>
+      </c>
       <c r="AB58" s="1">
         <v>0</v>
       </c>
@@ -3963,7 +4128,9 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
+      <c r="AA59" s="1">
+        <v>0</v>
+      </c>
       <c r="AB59" s="1">
         <v>0</v>
       </c>
@@ -4007,7 +4174,9 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
       <c r="AB60" s="1">
         <v>0</v>
       </c>
@@ -4051,7 +4220,9 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
+      <c r="AA61" s="1">
+        <v>0</v>
+      </c>
       <c r="AB61" s="1">
         <v>0</v>
       </c>
@@ -4096,7 +4267,9 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
+      <c r="AA62" s="1">
+        <v>0</v>
+      </c>
       <c r="AB62" s="1">
         <v>0</v>
       </c>
@@ -4141,7 +4314,9 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
+      <c r="AA63" s="1">
+        <v>0</v>
+      </c>
       <c r="AB63" s="1">
         <v>0</v>
       </c>
@@ -4186,7 +4361,9 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
+      <c r="AA64" s="1">
+        <v>0</v>
+      </c>
       <c r="AB64" s="1">
         <v>0</v>
       </c>
@@ -4231,7 +4408,9 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
+      <c r="AA65" s="1">
+        <v>0</v>
+      </c>
       <c r="AB65" s="1">
         <v>0</v>
       </c>
@@ -4270,52 +4449,52 @@
       <c r="A66" t="s">
         <v>92</v>
       </c>
-      <c r="U66" s="2">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2">
-        <v>0</v>
-      </c>
-      <c r="W66" s="2">
-        <v>0</v>
-      </c>
-      <c r="X66" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI66" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ66" s="2">
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66">
+        <v>0</v>
+      </c>
+      <c r="AI66">
+        <v>0</v>
+      </c>
+      <c r="AJ66">
         <v>0</v>
       </c>
       <c r="AK66" s="1">
@@ -4336,7 +4515,9 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
+      <c r="AA67" s="1">
+        <v>0</v>
+      </c>
       <c r="AB67" s="1">
         <v>0</v>
       </c>
@@ -4382,7 +4563,9 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
       <c r="AB68" s="1">
         <v>0</v>
       </c>
@@ -4428,7 +4611,9 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
-      <c r="AA69" s="1"/>
+      <c r="AA69" s="1">
+        <v>0</v>
+      </c>
       <c r="AB69" s="1">
         <v>0</v>
       </c>
@@ -4474,7 +4659,9 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
-      <c r="AA70" s="1"/>
+      <c r="AA70" s="1">
+        <v>0</v>
+      </c>
       <c r="AB70" s="1">
         <v>0</v>
       </c>
@@ -4520,7 +4707,9 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
-      <c r="AA71" s="1"/>
+      <c r="AA71" s="1">
+        <v>0</v>
+      </c>
       <c r="AB71" s="1">
         <v>0</v>
       </c>
@@ -4567,7 +4756,9 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
-      <c r="AA72" s="1"/>
+      <c r="AA72" s="1">
+        <v>0</v>
+      </c>
       <c r="AB72" s="1">
         <v>0</v>
       </c>
@@ -4614,7 +4805,9 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
+      <c r="AA73" s="1">
+        <v>0</v>
+      </c>
       <c r="AB73" s="1">
         <v>0</v>
       </c>
@@ -4661,7 +4854,9 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
-      <c r="AA74" s="1"/>
+      <c r="AA74" s="1">
+        <v>0</v>
+      </c>
       <c r="AB74" s="1">
         <v>0</v>
       </c>
@@ -4708,7 +4903,9 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
-      <c r="AA75" s="1"/>
+      <c r="AA75" s="1">
+        <v>0</v>
+      </c>
       <c r="AB75" s="1">
         <v>0</v>
       </c>
@@ -4755,7 +4952,9 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
-      <c r="AA76" s="1"/>
+      <c r="AA76" s="1">
+        <v>0</v>
+      </c>
       <c r="AB76" s="1">
         <v>0</v>
       </c>
@@ -4803,7 +5002,9 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
-      <c r="AA77" s="1"/>
+      <c r="AA77" s="1">
+        <v>0</v>
+      </c>
       <c r="AB77" s="1">
         <v>0</v>
       </c>
@@ -4851,7 +5052,9 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
       <c r="AB78" s="1">
         <v>0</v>
       </c>
@@ -4900,7 +5103,9 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
-      <c r="AA79" s="1"/>
+      <c r="AA79" s="1">
+        <v>0</v>
+      </c>
       <c r="AB79" s="1">
         <v>0</v>
       </c>
@@ -4949,7 +5154,9 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
-      <c r="AA80" s="1"/>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
       <c r="AB80" s="1">
         <v>0</v>
       </c>
@@ -4998,7 +5205,9 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
-      <c r="AA81" s="1"/>
+      <c r="AA81" s="1">
+        <v>0</v>
+      </c>
       <c r="AB81" s="1">
         <v>0</v>
       </c>
@@ -5047,7 +5256,9 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
-      <c r="AA82" s="1"/>
+      <c r="AA82" s="1">
+        <v>0</v>
+      </c>
       <c r="AB82" s="1">
         <v>0</v>
       </c>
@@ -5096,7 +5307,9 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
-      <c r="AA83" s="1"/>
+      <c r="AA83" s="1">
+        <v>0</v>
+      </c>
       <c r="AB83" s="1">
         <v>0</v>
       </c>
@@ -5146,7 +5359,9 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
-      <c r="AA84" s="1"/>
+      <c r="AA84" s="1">
+        <v>0</v>
+      </c>
       <c r="AB84" s="1">
         <v>0</v>
       </c>
@@ -5196,7 +5411,9 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
-      <c r="AA85" s="1"/>
+      <c r="AA85" s="1">
+        <v>0</v>
+      </c>
       <c r="AB85" s="1">
         <v>0</v>
       </c>
@@ -5246,7 +5463,9 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
-      <c r="AA86" s="1"/>
+      <c r="AA86" s="1">
+        <v>0</v>
+      </c>
       <c r="AB86" s="1">
         <v>0</v>
       </c>
@@ -5296,7 +5515,9 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
-      <c r="AA87" s="1"/>
+      <c r="AA87" s="1">
+        <v>0</v>
+      </c>
       <c r="AB87" s="1">
         <v>0</v>
       </c>
@@ -5347,7 +5568,9 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
-      <c r="AA88" s="1"/>
+      <c r="AA88" s="1">
+        <v>0</v>
+      </c>
       <c r="AB88" s="1">
         <v>0</v>
       </c>
@@ -5398,7 +5621,9 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
-      <c r="AA89" s="1"/>
+      <c r="AA89" s="1">
+        <v>0</v>
+      </c>
       <c r="AB89" s="1">
         <v>0</v>
       </c>
@@ -5449,7 +5674,9 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
-      <c r="AA90" s="1"/>
+      <c r="AA90" s="1">
+        <v>0</v>
+      </c>
       <c r="AB90" s="1">
         <v>0</v>
       </c>
@@ -5500,7 +5727,9 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
-      <c r="AA91" s="1"/>
+      <c r="AA91" s="1">
+        <v>0</v>
+      </c>
       <c r="AB91" s="1">
         <v>0</v>
       </c>
@@ -5551,7 +5780,9 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
-      <c r="AA92" s="1"/>
+      <c r="AA92" s="1">
+        <v>0</v>
+      </c>
       <c r="AB92" s="1">
         <v>0</v>
       </c>
@@ -5603,7 +5834,9 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
-      <c r="AA93" s="1"/>
+      <c r="AA93" s="1">
+        <v>0</v>
+      </c>
       <c r="AB93" s="1">
         <v>0</v>
       </c>
@@ -5655,7 +5888,9 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
-      <c r="AA94" s="1"/>
+      <c r="AA94" s="1">
+        <v>0</v>
+      </c>
       <c r="AB94" s="1">
         <v>0</v>
       </c>
@@ -5707,7 +5942,9 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
-      <c r="AA95" s="1"/>
+      <c r="AA95" s="1">
+        <v>0</v>
+      </c>
       <c r="AB95" s="1">
         <v>0</v>
       </c>
@@ -5759,7 +5996,9 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
-      <c r="AA96" s="1"/>
+      <c r="AA96" s="1">
+        <v>0</v>
+      </c>
       <c r="AB96" s="1">
         <v>0</v>
       </c>
@@ -5811,7 +6050,9 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
-      <c r="AA97" s="1"/>
+      <c r="AA97" s="1">
+        <v>0</v>
+      </c>
       <c r="AB97" s="1">
         <v>0</v>
       </c>
@@ -5864,7 +6105,9 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
-      <c r="AA98" s="1"/>
+      <c r="AA98" s="1">
+        <v>0</v>
+      </c>
       <c r="AB98" s="1">
         <v>0</v>
       </c>
@@ -5917,7 +6160,9 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
-      <c r="AA99" s="1"/>
+      <c r="AA99" s="1">
+        <v>0</v>
+      </c>
       <c r="AB99" s="1">
         <v>0</v>
       </c>
@@ -5970,7 +6215,9 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
-      <c r="AA100" s="1"/>
+      <c r="AA100" s="1">
+        <v>0</v>
+      </c>
       <c r="AB100" s="1">
         <v>0</v>
       </c>
@@ -6023,7 +6270,9 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
-      <c r="AA101" s="1"/>
+      <c r="AA101" s="1">
+        <v>0</v>
+      </c>
       <c r="AB101" s="1">
         <v>0</v>
       </c>
@@ -6077,7 +6326,9 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
-      <c r="AA102" s="1"/>
+      <c r="AA102" s="1">
+        <v>0</v>
+      </c>
       <c r="AB102" s="1">
         <v>0</v>
       </c>
@@ -6131,7 +6382,9 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
-      <c r="AA103" s="1"/>
+      <c r="AA103" s="1">
+        <v>0</v>
+      </c>
       <c r="AB103" s="1">
         <v>0</v>
       </c>
@@ -6186,7 +6439,9 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
-      <c r="AA104" s="1"/>
+      <c r="AA104" s="1">
+        <v>0</v>
+      </c>
       <c r="AB104" s="1">
         <v>0</v>
       </c>
@@ -6241,7 +6496,9 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
-      <c r="AA105" s="1"/>
+      <c r="AA105" s="1">
+        <v>0</v>
+      </c>
       <c r="AB105" s="1">
         <v>0</v>
       </c>
@@ -6296,7 +6553,9 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
-      <c r="AA106" s="1"/>
+      <c r="AA106" s="1">
+        <v>0</v>
+      </c>
       <c r="AB106" s="1">
         <v>0</v>
       </c>
@@ -6352,7 +6611,9 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
-      <c r="AA107" s="1"/>
+      <c r="AA107" s="1">
+        <v>0</v>
+      </c>
       <c r="AB107" s="1">
         <v>0</v>
       </c>
@@ -6408,7 +6669,9 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
+      <c r="AA108" s="1">
+        <v>0</v>
+      </c>
       <c r="AB108" s="1">
         <v>0</v>
       </c>
@@ -6464,7 +6727,9 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
-      <c r="AA109" s="1"/>
+      <c r="AA109" s="1">
+        <v>0</v>
+      </c>
       <c r="AB109" s="1">
         <v>0</v>
       </c>
@@ -6521,7 +6786,9 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
-      <c r="AA110" s="1"/>
+      <c r="AA110" s="1">
+        <v>0</v>
+      </c>
       <c r="AB110" s="1">
         <v>0</v>
       </c>
@@ -6578,7 +6845,9 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
-      <c r="AA111" s="1"/>
+      <c r="AA111" s="1">
+        <v>0</v>
+      </c>
       <c r="AB111" s="1">
         <v>0</v>
       </c>
@@ -6635,7 +6904,9 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
-      <c r="AA112" s="1"/>
+      <c r="AA112" s="1">
+        <v>0</v>
+      </c>
       <c r="AB112" s="1">
         <v>0</v>
       </c>
@@ -6693,7 +6964,9 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
-      <c r="AA113" s="1"/>
+      <c r="AA113" s="1">
+        <v>0</v>
+      </c>
       <c r="AB113" s="1">
         <v>0</v>
       </c>
@@ -6751,7 +7024,9 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
-      <c r="AA114" s="1"/>
+      <c r="AA114" s="1">
+        <v>0</v>
+      </c>
       <c r="AB114" s="1">
         <v>0</v>
       </c>
@@ -6810,7 +7085,9 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
-      <c r="AA115" s="1"/>
+      <c r="AA115" s="1">
+        <v>0</v>
+      </c>
       <c r="AB115" s="1">
         <v>0</v>
       </c>
@@ -6869,7 +7146,9 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
-      <c r="AA116" s="1"/>
+      <c r="AA116" s="1">
+        <v>0</v>
+      </c>
       <c r="AB116" s="1">
         <v>0</v>
       </c>
@@ -6928,7 +7207,9 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
-      <c r="AA117" s="1"/>
+      <c r="AA117" s="1">
+        <v>0</v>
+      </c>
       <c r="AB117" s="1">
         <v>0</v>
       </c>
@@ -6988,7 +7269,9 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
-      <c r="AA118" s="1"/>
+      <c r="AA118" s="1">
+        <v>0</v>
+      </c>
       <c r="AB118" s="1">
         <v>0</v>
       </c>
@@ -7048,7 +7331,9 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
-      <c r="AA119" s="1"/>
+      <c r="AA119" s="1">
+        <v>0</v>
+      </c>
       <c r="AB119" s="1">
         <v>0</v>
       </c>
@@ -7108,7 +7393,9 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
-      <c r="AA120" s="1"/>
+      <c r="AA120" s="1">
+        <v>0</v>
+      </c>
       <c r="AB120" s="1">
         <v>0</v>
       </c>
@@ -7169,7 +7456,9 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
-      <c r="AA121" s="1"/>
+      <c r="AA121" s="1">
+        <v>0</v>
+      </c>
       <c r="AB121" s="1">
         <v>0</v>
       </c>
@@ -7230,7 +7519,9 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
-      <c r="AA122" s="1"/>
+      <c r="AA122" s="1">
+        <v>0</v>
+      </c>
       <c r="AB122" s="1">
         <v>0</v>
       </c>
@@ -7291,7 +7582,9 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
-      <c r="AA123" s="1"/>
+      <c r="AA123" s="1">
+        <v>0</v>
+      </c>
       <c r="AB123" s="1">
         <v>0</v>
       </c>
@@ -7353,7 +7646,9 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
-      <c r="AA124" s="1"/>
+      <c r="AA124" s="1">
+        <v>0</v>
+      </c>
       <c r="AB124" s="1">
         <v>0</v>
       </c>
@@ -10936,7 +11231,58 @@
       </c>
       <c r="B2">
         <f>SUM(C2:C2:S2)</f>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -10945,6 +11291,57 @@
       </c>
       <c r="B3">
         <f>SUM(C3:C3:S3)</f>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
         <v>0</v>
       </c>
     </row>
@@ -10956,6 +11353,57 @@
         <f>SUM(C4:C4:S4)</f>
         <v>0</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -10963,6 +11411,57 @@
       </c>
       <c r="B5">
         <f>SUM(C5:C5:S5)</f>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>0</v>
       </c>
     </row>
@@ -10974,6 +11473,57 @@
         <f>SUM(C6:C6:S6)</f>
         <v>0</v>
       </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -10981,6 +11531,57 @@
       </c>
       <c r="B7">
         <f>SUM(C7:C7:S7)</f>
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>0</v>
       </c>
     </row>
@@ -10992,6 +11593,57 @@
         <f>SUM(C8:C8:S8)</f>
         <v>0</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -11001,6 +11653,57 @@
         <f>SUM(C9:C9:S9)</f>
         <v>0</v>
       </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -11010,6 +11713,57 @@
         <f>SUM(C10:C10:S10)</f>
         <v>0</v>
       </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -11019,6 +11773,57 @@
         <f>SUM(C11:C11:S11)</f>
         <v>0</v>
       </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -11028,6 +11833,57 @@
         <f>SUM(C12:C12:S12)</f>
         <v>0</v>
       </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -11037,6 +11893,57 @@
         <f>SUM(C13:C13:S13)</f>
         <v>0</v>
       </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -11046,6 +11953,57 @@
         <f>SUM(C14:C14:S14)</f>
         <v>0</v>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -11055,6 +12013,57 @@
         <f>SUM(C15:C15:S15)</f>
         <v>0</v>
       </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -11064,8 +12073,59 @@
         <f>SUM(C16:C16:S16)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -11073,8 +12133,59 @@
         <f>SUM(C17:C17:S17)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -11082,8 +12193,59 @@
         <f>SUM(C18:C18:S18)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -11091,8 +12253,59 @@
         <f>SUM(C19:C19:S19)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -11100,8 +12313,59 @@
         <f>SUM(C20:C20:S20)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -11109,8 +12373,59 @@
         <f>SUM(C21:C21:S21)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -11118,8 +12433,59 @@
         <f>SUM(C22:C22:S22)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -11127,13 +12493,115 @@
         <f>SUM(C23:C23:S23)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24">
         <f>SUM(C24:C24:S24)</f>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <v>0</v>
       </c>
     </row>
@@ -11144,139 +12612,346 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <f t="shared" ref="B3:B25" si="0">SUM(C3:R3)</f>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Files/Driver_Wins.xlsx
+++ b/Data_Files/Driver_Wins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D424367-A558-4430-B1E5-13DDB5A3378F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB3F664-3CC8-4AD2-81A6-3A78240BF6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" firstSheet="6" activeTab="13" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Wins" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="150">
   <si>
     <t>Driver</t>
   </si>
@@ -206,16 +206,7 @@
     <t>Fernando Alonso</t>
   </si>
   <si>
-    <t>Ralph Firman</t>
-  </si>
-  <si>
-    <t>Antônio Pizzonia</t>
-  </si>
-  <si>
     <t>Jos Verstappen</t>
-  </si>
-  <si>
-    <t>Justin Wilson</t>
   </si>
   <si>
     <t>Cristiano da Matta</t>
@@ -1084,13 +1075,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1133,13 +1124,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1601,7 +1592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL124"/>
+  <dimension ref="A1:AL121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -1989,6 +1980,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
       <c r="AA8">
         <v>0</v>
       </c>
@@ -2030,6 +2024,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
       <c r="AA9">
         <v>0</v>
       </c>
@@ -2071,6 +2068,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
       <c r="AA10">
         <v>0</v>
       </c>
@@ -2112,6 +2112,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
       <c r="AA11">
         <v>0</v>
       </c>
@@ -2153,6 +2156,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
       <c r="AA12">
         <v>0</v>
       </c>
@@ -2194,6 +2200,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
       <c r="AA13">
         <v>0</v>
       </c>
@@ -2232,6 +2241,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
       <c r="AA14">
         <v>0</v>
       </c>
@@ -2317,6 +2329,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
       <c r="AA16">
         <v>0</v>
       </c>
@@ -2358,6 +2373,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
       <c r="AA17">
         <v>0</v>
       </c>
@@ -2396,6 +2414,9 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
       <c r="AA18">
         <v>0</v>
       </c>
@@ -2435,7 +2456,10 @@
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>82</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
       </c>
       <c r="AA19">
         <v>0</v>
@@ -2478,6 +2502,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
       <c r="AA20">
         <v>0</v>
       </c>
@@ -2519,6 +2546,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
       <c r="AA21">
         <v>0</v>
       </c>
@@ -2558,7 +2588,10 @@
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
       </c>
       <c r="AA22">
         <v>0</v>
@@ -2601,6 +2634,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
       <c r="AA23">
         <v>0</v>
       </c>
@@ -2642,6 +2678,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
       <c r="AA24">
         <v>0</v>
       </c>
@@ -2727,31 +2766,34 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="1">
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
         <v>0</v>
       </c>
       <c r="AJ26" s="1">
@@ -2768,6 +2810,9 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
       <c r="AA27" s="1">
         <v>0</v>
       </c>
@@ -2807,7 +2852,10 @@
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -2821,19 +2869,19 @@
       <c r="AD28">
         <v>0</v>
       </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
+      <c r="AE28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="1">
         <v>0</v>
       </c>
       <c r="AJ28" s="1">
@@ -2848,7 +2896,10 @@
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
       </c>
       <c r="AA29" s="1">
         <v>0</v>
@@ -2889,7 +2940,10 @@
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
       </c>
       <c r="AA30" s="1">
         <v>0</v>
@@ -2930,18 +2984,21 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
+        <v>56</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="1">
         <v>0</v>
       </c>
       <c r="AE31" s="1">
@@ -2973,6 +3030,9 @@
       <c r="A32" t="s">
         <v>57</v>
       </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
       <c r="AA32" s="1">
         <v>0</v>
       </c>
@@ -3014,6 +3074,9 @@
       <c r="A33" t="s">
         <v>58</v>
       </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
       <c r="AA33" s="1">
         <v>0</v>
       </c>
@@ -3055,6 +3118,9 @@
       <c r="A34" t="s">
         <v>59</v>
       </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
@@ -3096,6 +3162,9 @@
       <c r="A35" t="s">
         <v>60</v>
       </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
       <c r="AA35" s="1">
         <v>0</v>
       </c>
@@ -3137,16 +3206,16 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="1">
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
         <v>0</v>
       </c>
       <c r="AE36" s="1">
@@ -3178,7 +3247,9 @@
       <c r="A37" t="s">
         <v>62</v>
       </c>
-      <c r="Z37" s="1"/>
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
       <c r="AA37" s="1">
         <v>0</v>
       </c>
@@ -3220,7 +3291,9 @@
       <c r="A38" t="s">
         <v>63</v>
       </c>
-      <c r="Z38" s="1"/>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
       <c r="AA38" s="1">
         <v>0</v>
       </c>
@@ -3262,13 +3335,20 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
-      <c r="AA39">
-        <v>0</v>
-      </c>
-      <c r="AB39">
-        <v>0</v>
-      </c>
-      <c r="AC39">
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1">
         <v>0</v>
       </c>
       <c r="AE39" s="1">
@@ -3300,23 +3380,22 @@
       <c r="A40" t="s">
         <v>65</v>
       </c>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="1">
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
         <v>0</v>
       </c>
       <c r="AG40" s="1">
@@ -3342,7 +3421,10 @@
       <c r="A41" t="s">
         <v>66</v>
       </c>
-      <c r="Z41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
       <c r="AA41" s="1">
         <v>0</v>
       </c>
@@ -3385,7 +3467,9 @@
         <v>67</v>
       </c>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
       <c r="AA42" s="1">
         <v>0</v>
       </c>
@@ -3427,19 +3511,26 @@
       <c r="A43" t="s">
         <v>68</v>
       </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="1">
         <v>0</v>
       </c>
       <c r="AG43" s="1">
@@ -3466,7 +3557,9 @@
         <v>69</v>
       </c>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
       <c r="AA44" s="1">
         <v>0</v>
       </c>
@@ -3509,7 +3602,9 @@
         <v>70</v>
       </c>
       <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
       <c r="AA45" s="1">
         <v>0</v>
       </c>
@@ -3551,8 +3646,11 @@
       <c r="A46" t="s">
         <v>71</v>
       </c>
+      <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
@@ -3594,8 +3692,11 @@
       <c r="A47" t="s">
         <v>72</v>
       </c>
+      <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
+      <c r="Z47" s="1">
+        <v>0</v>
+      </c>
       <c r="AA47" s="1">
         <v>0</v>
       </c>
@@ -3637,8 +3738,11 @@
       <c r="A48" t="s">
         <v>73</v>
       </c>
+      <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
+      <c r="Z48" s="1">
+        <v>0</v>
+      </c>
       <c r="AA48" s="1">
         <v>0</v>
       </c>
@@ -3682,7 +3786,9 @@
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
+      <c r="Z49" s="1">
+        <v>0</v>
+      </c>
       <c r="AA49" s="1">
         <v>0</v>
       </c>
@@ -3726,7 +3832,9 @@
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
       <c r="AA50" s="1">
         <v>0</v>
       </c>
@@ -3770,7 +3878,9 @@
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
       <c r="AA51" s="1">
         <v>0</v>
       </c>
@@ -3812,9 +3922,12 @@
       <c r="A52" t="s">
         <v>77</v>
       </c>
+      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
       <c r="AA52" s="1">
         <v>0</v>
       </c>
@@ -3856,9 +3969,12 @@
       <c r="A53" t="s">
         <v>78</v>
       </c>
+      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
+      <c r="Z53" s="1">
+        <v>0</v>
+      </c>
       <c r="AA53" s="1">
         <v>0</v>
       </c>
@@ -3900,9 +4016,12 @@
       <c r="A54" t="s">
         <v>79</v>
       </c>
+      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
       <c r="AA54" s="1">
         <v>0</v>
       </c>
@@ -3947,7 +4066,9 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
       <c r="AA55" s="1">
         <v>0</v>
       </c>
@@ -3992,7 +4113,9 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
+      <c r="Z56" s="1">
+        <v>0</v>
+      </c>
       <c r="AA56" s="1">
         <v>0</v>
       </c>
@@ -4032,12 +4155,15 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>82</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
       <c r="AA57" s="1">
         <v>0</v>
       </c>
@@ -4077,12 +4203,15 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>83</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
+      <c r="Z58" s="1">
+        <v>0</v>
+      </c>
       <c r="AA58" s="1">
         <v>0</v>
       </c>
@@ -4122,12 +4251,16 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>84</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
+      <c r="Z59" s="1">
+        <v>0</v>
+      </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
@@ -4169,11 +4302,14 @@
       <c r="A60" t="s">
         <v>86</v>
       </c>
+      <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
       <c r="AA60" s="1">
         <v>0</v>
       </c>
@@ -4215,11 +4351,14 @@
       <c r="A61" t="s">
         <v>87</v>
       </c>
+      <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
+      <c r="Z61" s="1">
+        <v>0</v>
+      </c>
       <c r="AA61" s="1">
         <v>0</v>
       </c>
@@ -4266,7 +4405,9 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
+      <c r="Z62" s="1">
+        <v>0</v>
+      </c>
       <c r="AA62" s="1">
         <v>0</v>
       </c>
@@ -4308,40 +4449,52 @@
       <c r="A63" t="s">
         <v>89</v>
       </c>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
-      <c r="AA63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ63" s="1">
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63">
+        <v>0</v>
+      </c>
+      <c r="AI63">
+        <v>0</v>
+      </c>
+      <c r="AJ63">
         <v>0</v>
       </c>
       <c r="AK63" s="1">
@@ -4355,12 +4508,15 @@
       <c r="A64" t="s">
         <v>90</v>
       </c>
+      <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
+      <c r="Z64" s="1">
+        <v>0</v>
+      </c>
       <c r="AA64" s="1">
         <v>0</v>
       </c>
@@ -4402,12 +4558,15 @@
       <c r="A65" t="s">
         <v>91</v>
       </c>
+      <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
+      <c r="Z65" s="1">
+        <v>0</v>
+      </c>
       <c r="AA65" s="1">
         <v>0</v>
       </c>
@@ -4449,52 +4608,43 @@
       <c r="A66" t="s">
         <v>92</v>
       </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66">
-        <v>0</v>
-      </c>
-      <c r="AI66">
-        <v>0</v>
-      </c>
-      <c r="AJ66">
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ66" s="1">
         <v>0</v>
       </c>
       <c r="AK66" s="1">
@@ -4514,7 +4664,9 @@
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
+      <c r="Z67" s="1">
+        <v>0</v>
+      </c>
       <c r="AA67" s="1">
         <v>0</v>
       </c>
@@ -4562,7 +4714,9 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
       <c r="AA68" s="1">
         <v>0</v>
       </c>
@@ -4604,13 +4758,16 @@
       <c r="A69" t="s">
         <v>95</v>
       </c>
+      <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
+      <c r="Z69" s="1">
+        <v>0</v>
+      </c>
       <c r="AA69" s="1">
         <v>0</v>
       </c>
@@ -4652,13 +4809,16 @@
       <c r="A70" t="s">
         <v>96</v>
       </c>
+      <c r="S70" s="1"/>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
+      <c r="Z70" s="1">
+        <v>0</v>
+      </c>
       <c r="AA70" s="1">
         <v>0</v>
       </c>
@@ -4700,13 +4860,16 @@
       <c r="A71" t="s">
         <v>97</v>
       </c>
+      <c r="S71" s="1"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
+      <c r="Z71" s="1">
+        <v>0</v>
+      </c>
       <c r="AA71" s="1">
         <v>0</v>
       </c>
@@ -4755,7 +4918,9 @@
       <c r="W72" s="1"/>
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
+      <c r="Z72" s="1">
+        <v>0</v>
+      </c>
       <c r="AA72" s="1">
         <v>0</v>
       </c>
@@ -4804,7 +4969,9 @@
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
+      <c r="Z73" s="1">
+        <v>0</v>
+      </c>
       <c r="AA73" s="1">
         <v>0</v>
       </c>
@@ -4846,6 +5013,7 @@
       <c r="A74" t="s">
         <v>100</v>
       </c>
+      <c r="R74" s="1"/>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
@@ -4853,7 +5021,9 @@
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
-      <c r="Z74" s="1"/>
+      <c r="Z74" s="1">
+        <v>0</v>
+      </c>
       <c r="AA74" s="1">
         <v>0</v>
       </c>
@@ -4895,6 +5065,7 @@
       <c r="A75" t="s">
         <v>101</v>
       </c>
+      <c r="R75" s="1"/>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
@@ -4902,7 +5073,9 @@
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
-      <c r="Z75" s="1"/>
+      <c r="Z75" s="1">
+        <v>0</v>
+      </c>
       <c r="AA75" s="1">
         <v>0</v>
       </c>
@@ -4944,6 +5117,8 @@
       <c r="A76" t="s">
         <v>102</v>
       </c>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -4951,7 +5126,9 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
       <c r="AA76" s="1">
         <v>0</v>
       </c>
@@ -4993,6 +5170,7 @@
       <c r="A77" t="s">
         <v>103</v>
       </c>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
@@ -5001,7 +5179,9 @@
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
+      <c r="Z77" s="1">
+        <v>0</v>
+      </c>
       <c r="AA77" s="1">
         <v>0</v>
       </c>
@@ -5043,6 +5223,7 @@
       <c r="A78" t="s">
         <v>104</v>
       </c>
+      <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
@@ -5051,7 +5232,9 @@
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
-      <c r="Z78" s="1"/>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
       <c r="AA78" s="1">
         <v>0</v>
       </c>
@@ -5102,7 +5285,9 @@
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
-      <c r="Z79" s="1"/>
+      <c r="Z79" s="1">
+        <v>0</v>
+      </c>
       <c r="AA79" s="1">
         <v>0</v>
       </c>
@@ -5153,7 +5338,9 @@
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
-      <c r="Z80" s="1"/>
+      <c r="Z80" s="1">
+        <v>0</v>
+      </c>
       <c r="AA80" s="1">
         <v>0</v>
       </c>
@@ -5195,6 +5382,7 @@
       <c r="A81" t="s">
         <v>107</v>
       </c>
+      <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -5204,7 +5392,9 @@
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
-      <c r="Z81" s="1"/>
+      <c r="Z81" s="1">
+        <v>0</v>
+      </c>
       <c r="AA81" s="1">
         <v>0</v>
       </c>
@@ -5246,6 +5436,7 @@
       <c r="A82" t="s">
         <v>108</v>
       </c>
+      <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -5255,7 +5446,9 @@
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
-      <c r="Z82" s="1"/>
+      <c r="Z82" s="1">
+        <v>0</v>
+      </c>
       <c r="AA82" s="1">
         <v>0</v>
       </c>
@@ -5297,6 +5490,7 @@
       <c r="A83" t="s">
         <v>109</v>
       </c>
+      <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -5306,7 +5500,9 @@
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
-      <c r="Z83" s="1"/>
+      <c r="Z83" s="1">
+        <v>0</v>
+      </c>
       <c r="AA83" s="1">
         <v>0</v>
       </c>
@@ -5358,7 +5554,9 @@
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
-      <c r="Z84" s="1"/>
+      <c r="Z84" s="1">
+        <v>0</v>
+      </c>
       <c r="AA84" s="1">
         <v>0</v>
       </c>
@@ -5400,6 +5598,7 @@
       <c r="A85" t="s">
         <v>111</v>
       </c>
+      <c r="O85" s="1"/>
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
@@ -5410,7 +5609,9 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
-      <c r="Z85" s="1"/>
+      <c r="Z85" s="1">
+        <v>0</v>
+      </c>
       <c r="AA85" s="1">
         <v>0</v>
       </c>
@@ -5452,6 +5653,7 @@
       <c r="A86" t="s">
         <v>112</v>
       </c>
+      <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
@@ -5462,7 +5664,9 @@
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
-      <c r="Z86" s="1"/>
+      <c r="Z86" s="1">
+        <v>0</v>
+      </c>
       <c r="AA86" s="1">
         <v>0</v>
       </c>
@@ -5504,6 +5708,7 @@
       <c r="A87" t="s">
         <v>113</v>
       </c>
+      <c r="O87" s="1"/>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
@@ -5514,7 +5719,9 @@
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
-      <c r="Z87" s="1"/>
+      <c r="Z87" s="1">
+        <v>0</v>
+      </c>
       <c r="AA87" s="1">
         <v>0</v>
       </c>
@@ -5567,7 +5774,9 @@
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
-      <c r="Z88" s="1"/>
+      <c r="Z88" s="1">
+        <v>0</v>
+      </c>
       <c r="AA88" s="1">
         <v>0</v>
       </c>
@@ -5620,7 +5829,9 @@
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
-      <c r="Z89" s="1"/>
+      <c r="Z89" s="1">
+        <v>0</v>
+      </c>
       <c r="AA89" s="1">
         <v>0</v>
       </c>
@@ -5662,6 +5873,7 @@
       <c r="A90" t="s">
         <v>116</v>
       </c>
+      <c r="N90" s="1"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -5673,7 +5885,9 @@
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
-      <c r="Z90" s="1"/>
+      <c r="Z90" s="1">
+        <v>0</v>
+      </c>
       <c r="AA90" s="1">
         <v>0</v>
       </c>
@@ -5715,6 +5929,7 @@
       <c r="A91" t="s">
         <v>117</v>
       </c>
+      <c r="N91" s="1"/>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
@@ -5726,7 +5941,9 @@
       <c r="W91" s="1"/>
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
-      <c r="Z91" s="1"/>
+      <c r="Z91" s="1">
+        <v>0</v>
+      </c>
       <c r="AA91" s="1">
         <v>0</v>
       </c>
@@ -5768,6 +5985,7 @@
       <c r="A92" t="s">
         <v>118</v>
       </c>
+      <c r="N92" s="1"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -5779,7 +5997,9 @@
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
-      <c r="Z92" s="1"/>
+      <c r="Z92" s="1">
+        <v>0</v>
+      </c>
       <c r="AA92" s="1">
         <v>0</v>
       </c>
@@ -5833,7 +6053,9 @@
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
-      <c r="Z93" s="1"/>
+      <c r="Z93" s="1">
+        <v>0</v>
+      </c>
       <c r="AA93" s="1">
         <v>0</v>
       </c>
@@ -5887,7 +6109,9 @@
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
-      <c r="Z94" s="1"/>
+      <c r="Z94" s="1">
+        <v>0</v>
+      </c>
       <c r="AA94" s="1">
         <v>0</v>
       </c>
@@ -5929,6 +6153,7 @@
       <c r="A95" t="s">
         <v>121</v>
       </c>
+      <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
@@ -5941,7 +6166,9 @@
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
-      <c r="Z95" s="1"/>
+      <c r="Z95" s="1">
+        <v>0</v>
+      </c>
       <c r="AA95" s="1">
         <v>0</v>
       </c>
@@ -5983,6 +6210,7 @@
       <c r="A96" t="s">
         <v>122</v>
       </c>
+      <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
@@ -5995,7 +6223,9 @@
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
-      <c r="Z96" s="1"/>
+      <c r="Z96" s="1">
+        <v>0</v>
+      </c>
       <c r="AA96" s="1">
         <v>0</v>
       </c>
@@ -6037,6 +6267,7 @@
       <c r="A97" t="s">
         <v>123</v>
       </c>
+      <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
@@ -6049,7 +6280,9 @@
       <c r="W97" s="1"/>
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
-      <c r="Z97" s="1"/>
+      <c r="Z97" s="1">
+        <v>0</v>
+      </c>
       <c r="AA97" s="1">
         <v>0</v>
       </c>
@@ -6104,7 +6337,9 @@
       <c r="W98" s="1"/>
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
-      <c r="Z98" s="1"/>
+      <c r="Z98" s="1">
+        <v>0</v>
+      </c>
       <c r="AA98" s="1">
         <v>0</v>
       </c>
@@ -6146,6 +6381,7 @@
       <c r="A99" t="s">
         <v>125</v>
       </c>
+      <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
@@ -6159,7 +6395,9 @@
       <c r="W99" s="1"/>
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
-      <c r="Z99" s="1"/>
+      <c r="Z99" s="1">
+        <v>0</v>
+      </c>
       <c r="AA99" s="1">
         <v>0</v>
       </c>
@@ -6201,6 +6439,7 @@
       <c r="A100" t="s">
         <v>126</v>
       </c>
+      <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
@@ -6214,7 +6453,9 @@
       <c r="W100" s="1"/>
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
-      <c r="Z100" s="1"/>
+      <c r="Z100" s="1">
+        <v>0</v>
+      </c>
       <c r="AA100" s="1">
         <v>0</v>
       </c>
@@ -6256,6 +6497,8 @@
       <c r="A101" t="s">
         <v>127</v>
       </c>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
@@ -6269,7 +6512,9 @@
       <c r="W101" s="1"/>
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
-      <c r="Z101" s="1"/>
+      <c r="Z101" s="1">
+        <v>0</v>
+      </c>
       <c r="AA101" s="1">
         <v>0</v>
       </c>
@@ -6311,6 +6556,7 @@
       <c r="A102" t="s">
         <v>128</v>
       </c>
+      <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -6325,7 +6571,9 @@
       <c r="W102" s="1"/>
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
-      <c r="Z102" s="1"/>
+      <c r="Z102" s="1">
+        <v>0</v>
+      </c>
       <c r="AA102" s="1">
         <v>0</v>
       </c>
@@ -6367,6 +6615,7 @@
       <c r="A103" t="s">
         <v>129</v>
       </c>
+      <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
@@ -6381,7 +6630,9 @@
       <c r="W103" s="1"/>
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
-      <c r="Z103" s="1"/>
+      <c r="Z103" s="1">
+        <v>0</v>
+      </c>
       <c r="AA103" s="1">
         <v>0</v>
       </c>
@@ -6423,6 +6674,7 @@
       <c r="A104" t="s">
         <v>130</v>
       </c>
+      <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
@@ -6438,7 +6690,9 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
-      <c r="Z104" s="1"/>
+      <c r="Z104" s="1">
+        <v>0</v>
+      </c>
       <c r="AA104" s="1">
         <v>0</v>
       </c>
@@ -6480,6 +6734,7 @@
       <c r="A105" t="s">
         <v>131</v>
       </c>
+      <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
@@ -6495,7 +6750,9 @@
       <c r="W105" s="1"/>
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
-      <c r="Z105" s="1"/>
+      <c r="Z105" s="1">
+        <v>0</v>
+      </c>
       <c r="AA105" s="1">
         <v>0</v>
       </c>
@@ -6537,6 +6794,7 @@
       <c r="A106" t="s">
         <v>132</v>
       </c>
+      <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -6552,7 +6810,9 @@
       <c r="W106" s="1"/>
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
-      <c r="Z106" s="1"/>
+      <c r="Z106" s="1">
+        <v>0</v>
+      </c>
       <c r="AA106" s="1">
         <v>0</v>
       </c>
@@ -6594,6 +6854,7 @@
       <c r="A107" t="s">
         <v>133</v>
       </c>
+      <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -6610,7 +6871,9 @@
       <c r="W107" s="1"/>
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
-      <c r="Z107" s="1"/>
+      <c r="Z107" s="1">
+        <v>0</v>
+      </c>
       <c r="AA107" s="1">
         <v>0</v>
       </c>
@@ -6652,6 +6915,7 @@
       <c r="A108" t="s">
         <v>134</v>
       </c>
+      <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -6668,7 +6932,9 @@
       <c r="W108" s="1"/>
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
-      <c r="Z108" s="1"/>
+      <c r="Z108" s="1">
+        <v>0</v>
+      </c>
       <c r="AA108" s="1">
         <v>0</v>
       </c>
@@ -6710,6 +6976,7 @@
       <c r="A109" t="s">
         <v>135</v>
       </c>
+      <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -6726,7 +6993,9 @@
       <c r="W109" s="1"/>
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
-      <c r="Z109" s="1"/>
+      <c r="Z109" s="1">
+        <v>0</v>
+      </c>
       <c r="AA109" s="1">
         <v>0</v>
       </c>
@@ -6768,6 +7037,7 @@
       <c r="A110" t="s">
         <v>136</v>
       </c>
+      <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
@@ -6785,7 +7055,9 @@
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
-      <c r="Z110" s="1"/>
+      <c r="Z110" s="1">
+        <v>0</v>
+      </c>
       <c r="AA110" s="1">
         <v>0</v>
       </c>
@@ -6827,6 +7099,7 @@
       <c r="A111" t="s">
         <v>137</v>
       </c>
+      <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
@@ -6844,7 +7117,9 @@
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
-      <c r="Z111" s="1"/>
+      <c r="Z111" s="1">
+        <v>0</v>
+      </c>
       <c r="AA111" s="1">
         <v>0</v>
       </c>
@@ -6886,6 +7161,8 @@
       <c r="A112" t="s">
         <v>138</v>
       </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
@@ -6903,7 +7180,9 @@
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
-      <c r="Z112" s="1"/>
+      <c r="Z112" s="1">
+        <v>0</v>
+      </c>
       <c r="AA112" s="1">
         <v>0</v>
       </c>
@@ -6945,6 +7224,7 @@
       <c r="A113" t="s">
         <v>139</v>
       </c>
+      <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6963,7 +7243,9 @@
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
-      <c r="Z113" s="1"/>
+      <c r="Z113" s="1">
+        <v>0</v>
+      </c>
       <c r="AA113" s="1">
         <v>0</v>
       </c>
@@ -7005,6 +7287,7 @@
       <c r="A114" t="s">
         <v>140</v>
       </c>
+      <c r="G114" s="1"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7023,7 +7306,9 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
-      <c r="Z114" s="1"/>
+      <c r="Z114" s="1">
+        <v>0</v>
+      </c>
       <c r="AA114" s="1">
         <v>0</v>
       </c>
@@ -7065,6 +7350,7 @@
       <c r="A115" t="s">
         <v>141</v>
       </c>
+      <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
@@ -7084,7 +7370,9 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
-      <c r="Z115" s="1"/>
+      <c r="Z115" s="1">
+        <v>0</v>
+      </c>
       <c r="AA115" s="1">
         <v>0</v>
       </c>
@@ -7126,6 +7414,7 @@
       <c r="A116" t="s">
         <v>142</v>
       </c>
+      <c r="F116" s="1"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
@@ -7145,7 +7434,9 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
-      <c r="Z116" s="1"/>
+      <c r="Z116" s="1">
+        <v>0</v>
+      </c>
       <c r="AA116" s="1">
         <v>0</v>
       </c>
@@ -7187,6 +7478,7 @@
       <c r="A117" t="s">
         <v>143</v>
       </c>
+      <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
@@ -7206,7 +7498,9 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
-      <c r="Z117" s="1"/>
+      <c r="Z117" s="1">
+        <v>0</v>
+      </c>
       <c r="AA117" s="1">
         <v>0</v>
       </c>
@@ -7248,6 +7542,7 @@
       <c r="A118" t="s">
         <v>144</v>
       </c>
+      <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -7268,7 +7563,9 @@
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
-      <c r="Z118" s="1"/>
+      <c r="Z118" s="1">
+        <v>0</v>
+      </c>
       <c r="AA118" s="1">
         <v>0</v>
       </c>
@@ -7310,6 +7607,7 @@
       <c r="A119" t="s">
         <v>145</v>
       </c>
+      <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
@@ -7330,7 +7628,9 @@
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
-      <c r="Z119" s="1"/>
+      <c r="Z119" s="1">
+        <v>0</v>
+      </c>
       <c r="AA119" s="1">
         <v>0</v>
       </c>
@@ -7372,6 +7672,7 @@
       <c r="A120" t="s">
         <v>146</v>
       </c>
+      <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -7392,7 +7693,9 @@
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
-      <c r="Z120" s="1"/>
+      <c r="Z120" s="1">
+        <v>0</v>
+      </c>
       <c r="AA120" s="1">
         <v>0</v>
       </c>
@@ -7434,6 +7737,7 @@
       <c r="A121" t="s">
         <v>147</v>
       </c>
+      <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -7455,7 +7759,9 @@
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
-      <c r="Z121" s="1"/>
+      <c r="Z121" s="1">
+        <v>0</v>
+      </c>
       <c r="AA121" s="1">
         <v>0</v>
       </c>
@@ -7490,196 +7796,6 @@
         <v>0</v>
       </c>
       <c r="AL121" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>148</v>
-      </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
-      <c r="U122" s="1"/>
-      <c r="V122" s="1"/>
-      <c r="W122" s="1"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="1"/>
-      <c r="Z122" s="1"/>
-      <c r="AA122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>149</v>
-      </c>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-      <c r="U123" s="1"/>
-      <c r="V123" s="1"/>
-      <c r="W123" s="1"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
-      <c r="AA123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>150</v>
-      </c>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1"/>
-      <c r="Q124" s="1"/>
-      <c r="R124" s="1"/>
-      <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
-      <c r="U124" s="1"/>
-      <c r="V124" s="1"/>
-      <c r="W124" s="1"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="1"/>
-      <c r="Z124" s="1"/>
-      <c r="AA124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL124" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8325,7 +8441,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -8439,7 +8555,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -8496,7 +8612,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -8553,7 +8669,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -8610,7 +8726,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -8667,7 +8783,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -9519,7 +9635,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -9639,7 +9755,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -9699,7 +9815,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -9759,7 +9875,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -9819,7 +9935,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
@@ -10912,7 +11028,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -11032,7 +11148,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -11092,7 +11208,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -12247,7 +12363,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
@@ -12776,7 +12892,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -12827,7 +12943,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -12848,7 +12964,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -12884,7 +13000,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -12902,7 +13018,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -12911,7 +13027,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -12920,7 +13036,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -12929,7 +13045,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -12938,7 +13054,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -12947,7 +13063,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -12992,7 +13108,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -13047,17 +13163,17 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -13067,12 +13183,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -13082,22 +13198,22 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -13120,7 +13236,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -13190,27 +13306,27 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -13220,12 +13336,12 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -13235,12 +13351,12 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -13263,7 +13379,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -13338,37 +13454,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -13378,22 +13494,22 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -13421,12 +13537,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -13441,12 +13557,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -13456,7 +13572,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -13466,7 +13582,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -13481,7 +13597,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -13501,12 +13617,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -13516,27 +13632,27 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -13559,7 +13675,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -13574,12 +13690,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -13589,12 +13705,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -13604,7 +13720,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -13614,12 +13730,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -13629,7 +13745,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -13639,7 +13755,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -13654,7 +13770,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -13664,7 +13780,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -13822,7 +13938,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -13837,7 +13953,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -13847,7 +13963,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -13857,12 +13973,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -13872,7 +13988,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -13882,7 +13998,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -13892,52 +14008,52 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -13960,12 +14076,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -13975,7 +14091,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -13990,12 +14106,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -14010,32 +14126,32 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -14050,12 +14166,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -14065,32 +14181,32 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -14113,7 +14229,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14128,12 +14244,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14143,7 +14259,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14153,12 +14269,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14168,27 +14284,27 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -14198,12 +14314,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -14218,37 +14334,37 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -14271,12 +14387,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -14286,7 +14402,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -14306,27 +14422,27 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -14336,57 +14452,57 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -14414,12 +14530,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -14429,7 +14545,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -14439,12 +14555,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14459,72 +14575,72 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -14547,32 +14663,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -14587,17 +14703,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -14607,57 +14723,57 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -14680,17 +14796,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -14700,7 +14816,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14710,47 +14826,47 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -14760,27 +14876,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -14803,27 +14919,27 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14833,22 +14949,22 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14858,17 +14974,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -14878,47 +14994,47 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -14941,17 +15057,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -14961,32 +15077,32 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14996,62 +15112,62 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -15074,12 +15190,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15089,87 +15205,87 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -15323,57 +15439,57 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -15383,42 +15499,42 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -15441,77 +15557,77 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -15521,37 +15637,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -15574,77 +15690,77 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -15654,27 +15770,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -15697,112 +15813,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -15825,112 +15941,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -15953,122 +16069,122 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -16092,107 +16208,107 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -16215,112 +16331,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -16570,7 +16686,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -16652,7 +16768,7 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
         <v>27</v>
@@ -16984,7 +17100,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -17098,7 +17214,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -17177,7 +17293,7 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
         <v>27</v>
@@ -17216,7 +17332,7 @@
         <v>32</v>
       </c>
       <c r="Q1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -17527,7 +17643,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -17647,7 +17763,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -17707,7 +17823,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -17793,7 +17909,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>32</v>
@@ -18236,7 +18352,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -18350,7 +18466,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -18407,7 +18523,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -18489,7 +18605,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -18525,7 +18641,7 @@
         <v>29</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -19076,7 +19192,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -19196,7 +19312,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -19256,7 +19372,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -19342,7 +19458,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -19378,7 +19494,7 @@
         <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -19899,7 +20015,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -20013,7 +20129,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -20070,7 +20186,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
